--- a/research/traditional_assets/database/data/hong_kong/hong_kong_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:AQ37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0203</v>
+        <v>-0.0418</v>
       </c>
       <c r="E2">
-        <v>0.469</v>
+        <v>-0.0441</v>
       </c>
       <c r="G2">
-        <v>0.4177602403441105</v>
+        <v>0.1454849088318545</v>
       </c>
       <c r="H2">
-        <v>0.4140518592319037</v>
+        <v>0.1394097567487312</v>
       </c>
       <c r="I2">
-        <v>0.298452818632079</v>
+        <v>-0.2306336402028712</v>
       </c>
       <c r="J2">
-        <v>0.2907338460814605</v>
+        <v>-0.2274886360182866</v>
       </c>
       <c r="K2">
-        <v>-48.402</v>
+        <v>-148.115</v>
       </c>
       <c r="L2">
-        <v>-0.08271569704747925</v>
+        <v>-0.4035072425075394</v>
       </c>
       <c r="M2">
-        <v>61.66100000000001</v>
+        <v>159.08</v>
       </c>
       <c r="N2">
-        <v>0.01078575939015794</v>
+        <v>0.02779884456902005</v>
       </c>
       <c r="O2">
-        <v>-1.273934961365233</v>
+        <v>-1.074030314282821</v>
       </c>
       <c r="P2">
-        <v>52.093</v>
+        <v>18.72</v>
       </c>
       <c r="Q2">
-        <v>0.009112122150329987</v>
+        <v>0.003271274643777064</v>
       </c>
       <c r="R2">
-        <v>-1.076257179455395</v>
+        <v>-0.1263882793775107</v>
       </c>
       <c r="S2">
-        <v>9.568000000000003</v>
+        <v>140.36</v>
       </c>
       <c r="T2">
-        <v>0.1551710157149576</v>
+        <v>0.8823233593160674</v>
       </c>
       <c r="U2">
-        <v>528.003</v>
+        <v>383.127</v>
       </c>
       <c r="V2">
-        <v>0.09235843264432235</v>
+        <v>0.06695051498110979</v>
       </c>
       <c r="W2">
-        <v>-0.05652853339506887</v>
+        <v>-0.2441821247892074</v>
       </c>
       <c r="X2">
-        <v>0.04958033345560378</v>
+        <v>0.07920747068752179</v>
       </c>
       <c r="Y2">
-        <v>-0.1061088668506727</v>
+        <v>-0.3233895954767292</v>
       </c>
       <c r="Z2">
-        <v>0.1527576558595037</v>
+        <v>0.135797864001565</v>
       </c>
       <c r="AA2">
-        <v>-0.009897286876982457</v>
+        <v>-0.3429791271347248</v>
       </c>
       <c r="AB2">
-        <v>0.04846598326881599</v>
+        <v>0.07854437574621463</v>
       </c>
       <c r="AC2">
-        <v>-0.06078597058701467</v>
+        <v>-0.4221811415847984</v>
       </c>
       <c r="AD2">
-        <v>844.6559999999999</v>
+        <v>830.385</v>
       </c>
       <c r="AE2">
-        <v>0.09025098216990701</v>
+        <v>0.02729837813867119</v>
       </c>
       <c r="AF2">
-        <v>844.74625098217</v>
+        <v>830.4122983781386</v>
       </c>
       <c r="AG2">
-        <v>316.7432509821699</v>
+        <v>447.2852983781386</v>
       </c>
       <c r="AH2">
-        <v>0.1287401828858961</v>
+        <v>0.1267233852112225</v>
       </c>
       <c r="AI2">
-        <v>0.2069966275214514</v>
+        <v>0.2429790436230802</v>
       </c>
       <c r="AJ2">
-        <v>0.05249627178294432</v>
+        <v>0.07249561806810259</v>
       </c>
       <c r="AK2">
-        <v>0.08914903662305274</v>
+        <v>0.1473998878225272</v>
       </c>
       <c r="AL2">
-        <v>20.234</v>
+        <v>25.637</v>
       </c>
       <c r="AM2">
-        <v>17.71</v>
+        <v>11.014</v>
       </c>
       <c r="AN2">
-        <v>3.311181848117541</v>
+        <v>63.7189226519337</v>
       </c>
       <c r="AO2">
-        <v>8.627458732825936</v>
+        <v>-3.303116589304521</v>
       </c>
       <c r="AP2">
-        <v>1.241682416470018</v>
+        <v>34.32207630280376</v>
       </c>
       <c r="AQ2">
-        <v>9.857029926595143</v>
+        <v>-7.688578173234065</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Asian Capital Resources (Holdings) Limited (SEHK:8025)</t>
+          <t>Sheng Yuan Holdings Limited (SEHK:851)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,25 +722,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.335</v>
+        <v>-0.0833</v>
       </c>
       <c r="G3">
-        <v>0.01387900355871886</v>
+        <v>0.2974607013301088</v>
       </c>
       <c r="H3">
-        <v>0.01387900355871886</v>
+        <v>0.2974607013301088</v>
       </c>
       <c r="I3">
-        <v>0.1257413997627521</v>
+        <v>0.3821039903264813</v>
       </c>
       <c r="J3">
-        <v>0.1257413997627521</v>
+        <v>0.1997361767615698</v>
       </c>
       <c r="K3">
-        <v>-0.381</v>
+        <v>1.04</v>
       </c>
       <c r="L3">
-        <v>-0.04519572953736655</v>
+        <v>0.1257557436517533</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,64 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>7.84</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.6173228346456693</v>
+      </c>
+      <c r="W3">
+        <v>-0.2321428571428571</v>
       </c>
       <c r="X3">
-        <v>0.0538885348458522</v>
+        <v>0.1274769118152398</v>
+      </c>
+      <c r="Y3">
+        <v>-0.359619768958097</v>
+      </c>
+      <c r="Z3">
+        <v>2.022004889975551</v>
+      </c>
+      <c r="AA3">
+        <v>0.4038675261169151</v>
       </c>
       <c r="AB3">
-        <v>0.05062841426342124</v>
+        <v>0.08990456335307645</v>
+      </c>
+      <c r="AC3">
+        <v>0.3139629627638386</v>
       </c>
       <c r="AD3">
-        <v>2.67</v>
+        <v>18.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.67</v>
+        <v>18.9</v>
       </c>
       <c r="AG3">
-        <v>2.67</v>
+        <v>11.06</v>
       </c>
       <c r="AH3">
-        <v>0.1714836223506744</v>
+        <v>0.5981012658227848</v>
       </c>
       <c r="AI3">
-        <v>0.6935064935064935</v>
+        <v>1.219354838709678</v>
       </c>
       <c r="AJ3">
-        <v>0.1714836223506744</v>
+        <v>0.4654882154882155</v>
       </c>
       <c r="AK3">
-        <v>0.6935064935064935</v>
+        <v>1.443864229765013</v>
       </c>
       <c r="AL3">
-        <v>0.058</v>
+        <v>1.19</v>
       </c>
       <c r="AM3">
-        <v>0.05300000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="AN3">
-        <v>2.383928571428571</v>
+        <v>5.815384615384615</v>
       </c>
       <c r="AO3">
-        <v>18.27586206896552</v>
+        <v>2.65546218487395</v>
       </c>
       <c r="AP3">
-        <v>2.383928571428571</v>
+        <v>3.403076923076923</v>
       </c>
       <c r="AQ3">
-        <v>20</v>
+        <v>2.65546218487395</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vinco Financial Group Limited (SEHK:8340)</t>
+          <t>Value Partners Group Limited (SEHK:806)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,100 +850,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00859</v>
+        <v>-0.0764</v>
       </c>
       <c r="G4">
-        <v>-0.1705555555555555</v>
+        <v>0.3933437744714173</v>
       </c>
       <c r="H4">
-        <v>-0.1705555555555555</v>
+        <v>0.3758809710258418</v>
       </c>
       <c r="I4">
-        <v>0.2427777777777778</v>
+        <v>0.1213782302270947</v>
       </c>
       <c r="J4">
-        <v>0.2280981912144703</v>
+        <v>0.1213782302270947</v>
       </c>
       <c r="K4">
-        <v>0.405</v>
+        <v>-23</v>
       </c>
       <c r="L4">
-        <v>0.225</v>
+        <v>-0.1801096319498825</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>25.527</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03783459315251222</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>-1.109869565217391</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>18.267</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02707425522454424</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>-0.7942173913043478</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>7.260000000000002</v>
+      </c>
+      <c r="T4">
+        <v>0.2844047479139735</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>204.4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.3029494590188231</v>
+      </c>
+      <c r="W4">
+        <v>-0.03560371517027864</v>
       </c>
       <c r="X4">
-        <v>0.05047403263849654</v>
+        <v>0.07906070076279677</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1146644159330754</v>
+      </c>
+      <c r="Z4">
+        <v>0.3083051665861903</v>
+      </c>
+      <c r="AA4">
+        <v>0.0374215354901014</v>
       </c>
       <c r="AB4">
-        <v>0.05288651464674466</v>
+        <v>0.07848473401109766</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04106319852099626</v>
       </c>
       <c r="AD4">
-        <v>0.39</v>
+        <v>14.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.39</v>
+        <v>14.7</v>
       </c>
       <c r="AG4">
-        <v>0.39</v>
+        <v>-189.7</v>
       </c>
       <c r="AH4">
-        <v>0.07692307692307694</v>
+        <v>0.02132288946910357</v>
       </c>
       <c r="AI4">
-        <v>0.1083333333333333</v>
+        <v>0.0242094861660079</v>
       </c>
       <c r="AJ4">
-        <v>0.07692307692307694</v>
+        <v>-0.3911340206185567</v>
       </c>
       <c r="AK4">
-        <v>0.1083333333333333</v>
+        <v>-0.470953326713009</v>
       </c>
       <c r="AL4">
-        <v>0.007</v>
+        <v>0.603</v>
       </c>
       <c r="AM4">
-        <v>0.007</v>
+        <v>0.603</v>
       </c>
       <c r="AN4">
-        <v>0.8057851239669422</v>
+        <v>0.8647058823529411</v>
       </c>
       <c r="AO4">
-        <v>62.42857142857143</v>
+        <v>25.70480928689884</v>
       </c>
       <c r="AP4">
-        <v>0.8057851239669422</v>
+        <v>-11.15882352941177</v>
       </c>
       <c r="AQ4">
-        <v>62.42857142857143</v>
+        <v>25.70480928689884</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>True Partner Capital Holding Limited (SEHK:8657)</t>
+          <t>CST Group Limited (SEHK:985)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,110 +980,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.452</v>
+      </c>
       <c r="G5">
-        <v>0.6179245283018868</v>
+        <v>0.1934865900383142</v>
       </c>
       <c r="H5">
-        <v>0.6179245283018868</v>
+        <v>0.1934865900383142</v>
       </c>
       <c r="I5">
-        <v>0.02278543508287546</v>
+        <v>0.1698595146871009</v>
       </c>
       <c r="J5">
-        <v>0.02278543508287546</v>
+        <v>0.1698595146871009</v>
       </c>
       <c r="K5">
-        <v>-0.5610000000000001</v>
+        <v>-72.40000000000001</v>
       </c>
       <c r="L5">
-        <v>-0.0529245283018868</v>
+        <v>-0.4623243933588762</v>
       </c>
       <c r="M5">
-        <v>1.2</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02515723270440251</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-2.13903743315508</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.2</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02515723270440251</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-2.13903743315508</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.5835370823145883</v>
+      </c>
+      <c r="W5">
+        <v>-0.2441821247892074</v>
       </c>
       <c r="X5">
-        <v>0.04832693733719164</v>
+        <v>0.2086065461055711</v>
+      </c>
+      <c r="Y5">
+        <v>-0.4527886708947786</v>
       </c>
       <c r="Z5">
-        <v>610.1793829160557</v>
+        <v>0.216507673164662</v>
       </c>
       <c r="AA5">
-        <v>13.9032027183428</v>
+        <v>0.03677588828978294</v>
       </c>
       <c r="AB5">
-        <v>0.04822620800990453</v>
+        <v>0.08370626453053831</v>
       </c>
       <c r="AC5">
-        <v>13.85497651033289</v>
+        <v>-0.04693037624075537</v>
       </c>
       <c r="AD5">
-        <v>0.249</v>
+        <v>484.1</v>
       </c>
       <c r="AE5">
-        <v>0.01737194060760043</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.2663719406076004</v>
+        <v>484.1</v>
       </c>
       <c r="AG5">
-        <v>0.2663719406076004</v>
+        <v>412.5</v>
       </c>
       <c r="AH5">
-        <v>0.005553305989817713</v>
+        <v>0.7977916941331575</v>
       </c>
       <c r="AI5">
-        <v>0.009390412745250593</v>
+        <v>0.6928581651638758</v>
       </c>
       <c r="AJ5">
-        <v>0.005553305989817713</v>
+        <v>0.7707399103139013</v>
       </c>
       <c r="AK5">
-        <v>0.009390412745250593</v>
+        <v>0.6577898261840217</v>
       </c>
       <c r="AL5">
-        <v>0.011</v>
+        <v>10.4</v>
       </c>
       <c r="AM5">
-        <v>0.011</v>
+        <v>10.092</v>
       </c>
       <c r="AN5">
-        <v>0.680327868852459</v>
+        <v>8.261092150170649</v>
       </c>
       <c r="AO5">
-        <v>20.63636363636364</v>
+        <v>2.557692307692308</v>
       </c>
       <c r="AP5">
-        <v>0.7277921874524602</v>
+        <v>7.039249146757679</v>
       </c>
       <c r="AQ5">
-        <v>20.63636363636364</v>
+        <v>2.635751089972255</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sheng Yuan Holdings Limited (SEHK:851)</t>
+          <t>Wealthking Investments Limited (SEHK:1140)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,25 +1109,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.163</v>
+        <v>0.0597</v>
+      </c>
+      <c r="E6">
+        <v>-0.0441</v>
       </c>
       <c r="G6">
-        <v>0.3801324503311259</v>
+        <v>0.7245508982035929</v>
       </c>
       <c r="H6">
-        <v>0.3801324503311259</v>
+        <v>0.7245508982035929</v>
       </c>
       <c r="I6">
-        <v>0.614569536423841</v>
+        <v>0.6347305389221557</v>
       </c>
       <c r="J6">
-        <v>0.5077438368988593</v>
+        <v>0.6347305389221557</v>
       </c>
       <c r="K6">
-        <v>3.16</v>
+        <v>30.3</v>
       </c>
       <c r="L6">
-        <v>0.4185430463576159</v>
+        <v>1.81437125748503</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,73 +1154,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>9.630000000000001</v>
+        <v>3.51</v>
       </c>
       <c r="V6">
-        <v>0.5041884816753927</v>
+        <v>0.007017193122750899</v>
       </c>
       <c r="W6">
-        <v>-0.3301985370950888</v>
+        <v>0.04606263301915476</v>
       </c>
       <c r="X6">
-        <v>0.07448718111197983</v>
+        <v>0.09045374578462688</v>
       </c>
       <c r="Y6">
-        <v>-0.4046857182070687</v>
+        <v>-0.04439111276547212</v>
       </c>
       <c r="Z6">
-        <v>7.25961538461539</v>
+        <v>0.02382990867579909</v>
       </c>
       <c r="AA6">
-        <v>3.686024969794606</v>
+        <v>0.01512557077625571</v>
       </c>
       <c r="AB6">
-        <v>0.05163086945715668</v>
+        <v>0.08099781653500006</v>
       </c>
       <c r="AC6">
-        <v>3.634394100337449</v>
+        <v>-0.06587224575874435</v>
       </c>
       <c r="AD6">
-        <v>18.2</v>
+        <v>183.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>18.2</v>
+        <v>183.5</v>
       </c>
       <c r="AG6">
-        <v>8.569999999999999</v>
+        <v>179.99</v>
       </c>
       <c r="AH6">
-        <v>0.4879356568364611</v>
+        <v>0.2683925698405734</v>
       </c>
       <c r="AI6">
-        <v>1.326530612244898</v>
+        <v>0.1297461641801598</v>
       </c>
       <c r="AJ6">
-        <v>0.3097217202746657</v>
+        <v>0.2646172393007836</v>
       </c>
       <c r="AK6">
-        <v>2.095354523227384</v>
+        <v>0.1275810007159109</v>
       </c>
       <c r="AL6">
-        <v>0.805</v>
+        <v>6.81</v>
       </c>
       <c r="AM6">
-        <v>0.805</v>
+        <v>6.81</v>
       </c>
       <c r="AN6">
-        <v>3.847780126849894</v>
+        <v>16.23893805309734</v>
       </c>
       <c r="AO6">
-        <v>5.763975155279502</v>
+        <v>1.556534508076358</v>
       </c>
       <c r="AP6">
-        <v>1.81183932346723</v>
+        <v>15.9283185840708</v>
       </c>
       <c r="AQ6">
-        <v>5.763975155279502</v>
+        <v>1.556534508076358</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Value Partners Group Limited (SEHK:806)</t>
+          <t>Central Wealth Group Holdings Limited (SEHK:139)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1197,119 +1239,101 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.118</v>
-      </c>
       <c r="G7">
-        <v>0.4861594609769792</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.4800673778775968</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.5015507021327466</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.4324899695883931</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>188.5</v>
+        <v>-37</v>
       </c>
       <c r="L7">
-        <v>0.5291970802919708</v>
+        <v>-1.048158640226629</v>
       </c>
       <c r="M7">
-        <v>50.53700000000001</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05475891212482394</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.2681007957559682</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>50.2</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05439375880377072</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.2663129973474801</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0.3370000000000033</v>
-      </c>
-      <c r="T7">
-        <v>0.006668381581811411</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>249.7</v>
+        <v>12.7</v>
       </c>
       <c r="V7">
-        <v>0.2705601907032181</v>
+        <v>0.05390492359932088</v>
       </c>
       <c r="W7">
-        <v>0.3559962228517469</v>
+        <v>-0.24983119513842</v>
       </c>
       <c r="X7">
-        <v>0.04871023103614652</v>
+        <v>0.08529229567557928</v>
       </c>
       <c r="Y7">
-        <v>0.3072859918156004</v>
+        <v>-0.3351234908139993</v>
       </c>
       <c r="Z7">
-        <v>1.150281985632537</v>
+        <v>0.1641097164109716</v>
       </c>
       <c r="AA7">
-        <v>0.4974854209842925</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04823441744952626</v>
+        <v>0.08479677217555831</v>
       </c>
       <c r="AC7">
-        <v>0.4492510035347663</v>
+        <v>-0.08479677217555831</v>
       </c>
       <c r="AD7">
-        <v>17.9</v>
+        <v>49.6</v>
       </c>
       <c r="AE7">
-        <v>0.06319950157824035</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>17.96319950157824</v>
+        <v>49.6</v>
       </c>
       <c r="AG7">
-        <v>-231.7368004984218</v>
+        <v>36.90000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.01909225433739382</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="AI7">
-        <v>0.02705451072448412</v>
+        <v>0.2618796198521647</v>
       </c>
       <c r="AJ7">
-        <v>-0.3352852129070749</v>
+        <v>0.1354128440366973</v>
       </c>
       <c r="AK7">
-        <v>-0.5593950917610747</v>
+        <v>0.2088285229202037</v>
       </c>
       <c r="AL7">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.406</v>
-      </c>
-      <c r="AN7">
-        <v>0.09896884416553782</v>
-      </c>
-      <c r="AO7">
-        <v>439.9014778325123</v>
-      </c>
-      <c r="AP7">
-        <v>-1.281269457874225</v>
-      </c>
-      <c r="AQ7">
-        <v>439.9014778325123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>China Investment Fund Company Limited (SEHK:612)</t>
+          <t>UBA Investments Limited (SEHK:768)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,23 +1352,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D8">
+        <v>-0.289</v>
+      </c>
       <c r="G8">
-        <v>0.946969696969697</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.946969696969697</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.7765151515151516</v>
+        <v>-0.2086811352253756</v>
       </c>
       <c r="J8">
-        <v>0.7765151515151516</v>
+        <v>-0.2086811352253756</v>
       </c>
       <c r="K8">
-        <v>39.4</v>
+        <v>-1.67</v>
       </c>
       <c r="L8">
-        <v>0.7462121212121212</v>
+        <v>-2.787979966611018</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1353,7 +1380,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1362,79 +1389,67 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>20.3</v>
+        <v>0.613</v>
       </c>
       <c r="V8">
-        <v>0.03574572988202149</v>
+        <v>0.1211462450592885</v>
       </c>
       <c r="W8">
-        <v>0.4696066746126341</v>
+        <v>-0.1265151515151515</v>
       </c>
       <c r="X8">
-        <v>0.0493835543987524</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y8">
-        <v>0.4202231202138816</v>
+        <v>-0.2048564951962619</v>
       </c>
       <c r="Z8">
-        <v>0.6118192352259558</v>
+        <v>0.04702834262385177</v>
       </c>
       <c r="AA8">
-        <v>0.4750869061413673</v>
+        <v>-0.009813927926513307</v>
       </c>
       <c r="AB8">
-        <v>0.05074670104895405</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC8">
-        <v>0.4243402050924132</v>
+        <v>-0.08815527160762371</v>
       </c>
       <c r="AD8">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>4.599999999999998</v>
+        <v>-0.613</v>
       </c>
       <c r="AH8">
-        <v>0.04200404858299595</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.1526670754138565</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.008034934497816591</v>
+        <v>-0.1378457387002474</v>
       </c>
       <c r="AK8">
-        <v>0.03221288515406161</v>
+        <v>-0.05682766292759803</v>
       </c>
       <c r="AL8">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.87</v>
-      </c>
-      <c r="AN8">
-        <v>0.5804195804195804</v>
-      </c>
-      <c r="AO8">
-        <v>14.28571428571428</v>
-      </c>
-      <c r="AP8">
-        <v>0.1072261072261072</v>
-      </c>
-      <c r="AQ8">
-        <v>14.28571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1445,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital VC Limited (SEHK:2324)</t>
+          <t>Walnut Capital Limited (SEHK:905)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1453,23 +1468,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0401</v>
+      </c>
       <c r="G9">
-        <v>0.8289719626168224</v>
+        <v>-2.069392812887236</v>
       </c>
       <c r="H9">
-        <v>0.8289719626168224</v>
+        <v>-2.069392812887236</v>
       </c>
       <c r="I9">
-        <v>0.8289719626168224</v>
+        <v>-2.168525402726146</v>
       </c>
       <c r="J9">
-        <v>0.8289719626168224</v>
+        <v>-2.168525402726146</v>
       </c>
       <c r="K9">
-        <v>8.06</v>
+        <v>-18.1</v>
       </c>
       <c r="L9">
-        <v>0.7532710280373833</v>
+        <v>-22.42874845105328</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1478,7 +1496,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1487,79 +1505,79 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1.53</v>
+        <v>0.478</v>
       </c>
       <c r="V9">
-        <v>0.09683544303797469</v>
+        <v>0.03229729729729729</v>
       </c>
       <c r="W9">
-        <v>0.1392055267702936</v>
+        <v>-0.4480198019801981</v>
       </c>
       <c r="X9">
-        <v>0.04817272237335087</v>
+        <v>0.08532399765258109</v>
       </c>
       <c r="Y9">
-        <v>0.09103280439694275</v>
+        <v>-0.5333437996327792</v>
       </c>
       <c r="Z9">
-        <v>0.186476124085047</v>
+        <v>0.01784766454352442</v>
       </c>
       <c r="AA9">
-        <v>0.1545834785639596</v>
+        <v>-0.03870311394196745</v>
       </c>
       <c r="AB9">
-        <v>0.04817272237335087</v>
+        <v>0.08006916545070474</v>
       </c>
       <c r="AC9">
-        <v>0.1064107561906087</v>
+        <v>-0.1187722793926722</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AG9">
-        <v>-1.53</v>
+        <v>2.652</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.1745677635248187</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.1255515443241075</v>
       </c>
       <c r="AJ9">
-        <v>-0.1072179397337071</v>
+        <v>0.1519596607838643</v>
       </c>
       <c r="AK9">
-        <v>-0.02315725745421523</v>
+        <v>0.108457385898904</v>
       </c>
       <c r="AL9">
-        <v>0.214</v>
+        <v>0.104</v>
       </c>
       <c r="AM9">
-        <v>0.214</v>
+        <v>0.104</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>-1.874251497005988</v>
       </c>
       <c r="AO9">
-        <v>41.44859813084112</v>
+        <v>-16.82692307692308</v>
       </c>
       <c r="AP9">
-        <v>-0.1724915445321308</v>
+        <v>-1.588023952095809</v>
       </c>
       <c r="AQ9">
-        <v>41.44859813084112</v>
+        <v>-16.82692307692308</v>
       </c>
     </row>
     <row r="10">
@@ -1570,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OCI International Holdings Limited (SEHK:329)</t>
+          <t>Harbour Digital Asset Capital Limited (SEHK:913)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,22 +1597,22 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.1610091743119266</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.1610091743119266</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.1995412844036697</v>
+        <v>-7.748917748917749</v>
       </c>
       <c r="J10">
-        <v>0.1307952117632273</v>
+        <v>-7.748917748917749</v>
       </c>
       <c r="K10">
-        <v>0.988</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L10">
-        <v>0.04532110091743119</v>
+        <v>-40.56277056277056</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1603,7 +1621,7 @@
         <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1612,79 +1630,67 @@
         <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>30.5</v>
+        <v>1.28</v>
       </c>
       <c r="V10">
-        <v>0.04650808173223544</v>
+        <v>0.06124401913875599</v>
       </c>
       <c r="W10">
-        <v>0.03742424242424243</v>
+        <v>-0.2928125</v>
       </c>
       <c r="X10">
-        <v>0.04977711251245517</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y10">
-        <v>-0.01235287008821274</v>
+        <v>-0.3711538436811104</v>
       </c>
       <c r="Z10">
-        <v>0.2749747729566095</v>
+        <v>0.007633840052875082</v>
       </c>
       <c r="AA10">
-        <v>0.0359653836584051</v>
+        <v>-0.05915399867812293</v>
       </c>
       <c r="AB10">
-        <v>0.04856186516755982</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC10">
-        <v>-0.01259648150915472</v>
+        <v>-0.1374953423592333</v>
       </c>
       <c r="AD10">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>7.600000000000001</v>
+        <v>-1.28</v>
       </c>
       <c r="AH10">
-        <v>0.05490704712494596</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.3720703125</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.01145613506180284</v>
+        <v>-0.06523955147808359</v>
       </c>
       <c r="AK10">
-        <v>0.1057023643949931</v>
+        <v>-0.05683836589698046</v>
       </c>
       <c r="AL10">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.757</v>
-      </c>
-      <c r="AN10">
-        <v>8.619909502262443</v>
-      </c>
-      <c r="AO10">
-        <v>2.457627118644067</v>
-      </c>
-      <c r="AP10">
-        <v>1.719457013574661</v>
-      </c>
-      <c r="AQ10">
-        <v>2.475811041548093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1695,7 +1701,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wealthking Investments Limited (SEHK:1140)</t>
+          <t>China Innovation Investment Limited (SEHK:1217)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1703,29 +1709,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.125</v>
-      </c>
-      <c r="E11">
-        <v>0.469</v>
-      </c>
-      <c r="G11">
-        <v>0.979591836734694</v>
-      </c>
-      <c r="H11">
-        <v>0.979591836734694</v>
-      </c>
-      <c r="I11">
-        <v>1.306122448979592</v>
-      </c>
-      <c r="J11">
-        <v>1.306122448979592</v>
-      </c>
       <c r="K11">
-        <v>18.5</v>
-      </c>
-      <c r="L11">
-        <v>1.258503401360544</v>
+        <v>-5.35</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1734,7 +1719,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1743,79 +1728,73 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>16.3</v>
+        <v>1.28</v>
       </c>
       <c r="V11">
-        <v>0.03911687065034797</v>
+        <v>0.07804878048780489</v>
       </c>
       <c r="W11">
-        <v>0.03139850644942294</v>
+        <v>-0.06257309941520467</v>
       </c>
       <c r="X11">
-        <v>0.0521026777001511</v>
+        <v>0.07858091841372464</v>
       </c>
       <c r="Y11">
-        <v>-0.02070417125072815</v>
+        <v>-0.1411540178289293</v>
       </c>
       <c r="Z11">
-        <v>0.0234016811003566</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0.03056546102903719</v>
+        <v>-0.06354722010662604</v>
       </c>
       <c r="AB11">
-        <v>0.04937258991619643</v>
+        <v>0.07834347035023843</v>
       </c>
       <c r="AC11">
-        <v>-0.01880712888715924</v>
+        <v>-0.1418906904568645</v>
       </c>
       <c r="AD11">
-        <v>59.3</v>
+        <v>0.119</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>59.3</v>
+        <v>0.119</v>
       </c>
       <c r="AG11">
-        <v>43</v>
+        <v>-1.161</v>
       </c>
       <c r="AH11">
-        <v>0.1245798319327731</v>
+        <v>0.00720382589745142</v>
       </c>
       <c r="AI11">
-        <v>0.08269418491144889</v>
+        <v>0.00152136948823176</v>
       </c>
       <c r="AJ11">
-        <v>0.09353926473787252</v>
+        <v>-0.0761861014502264</v>
       </c>
       <c r="AK11">
-        <v>0.06135844748858448</v>
+        <v>-0.01508987639558612</v>
       </c>
       <c r="AL11">
-        <v>3.38</v>
+        <v>0.014</v>
       </c>
       <c r="AM11">
-        <v>3.38</v>
-      </c>
-      <c r="AN11">
-        <v>2.950248756218905</v>
+        <v>0.014</v>
       </c>
       <c r="AO11">
-        <v>5.680473372781065</v>
-      </c>
-      <c r="AP11">
-        <v>2.139303482587064</v>
+        <v>-381.4285714285714</v>
       </c>
       <c r="AQ11">
-        <v>5.680473372781065</v>
+        <v>-381.4285714285714</v>
       </c>
     </row>
     <row r="12">
@@ -1826,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBA Investments Limited (SEHK:768)</t>
+          <t>China Investment Fund Company Limited (SEHK:612)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1835,22 +1814,22 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>5.253623188405798</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>5.253623188405798</v>
       </c>
       <c r="I12">
-        <v>0.05227655986509275</v>
+        <v>-9.420289855072465</v>
       </c>
       <c r="J12">
-        <v>0.05227655986509275</v>
+        <v>-9.420289855072465</v>
       </c>
       <c r="K12">
-        <v>1.07</v>
+        <v>-7.47</v>
       </c>
       <c r="L12">
-        <v>1.804384485666105</v>
+        <v>-5.41304347826087</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1859,7 +1838,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1868,67 +1847,79 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.463</v>
+        <v>18.3</v>
       </c>
       <c r="V12">
-        <v>0.06604850213980029</v>
+        <v>0.02954949136121428</v>
       </c>
       <c r="W12">
-        <v>0.08770491803278689</v>
+        <v>-0.0540520984081042</v>
       </c>
       <c r="X12">
-        <v>0.04817272237335087</v>
+        <v>0.0795568904290532</v>
       </c>
       <c r="Y12">
-        <v>0.03953219565943602</v>
+        <v>-0.1336089888371574</v>
       </c>
       <c r="Z12">
-        <v>0.05050246976664963</v>
+        <v>0.009663865546218488</v>
       </c>
       <c r="AA12">
-        <v>0.002640095384091296</v>
+        <v>-0.09103641456582634</v>
       </c>
       <c r="AB12">
-        <v>0.04817272237335087</v>
+        <v>0.07858012810039418</v>
       </c>
       <c r="AC12">
-        <v>-0.04553262698925958</v>
+        <v>-0.1696165426662205</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AG12">
-        <v>-0.463</v>
+        <v>4.5</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.03550848777448996</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.1413515189088655</v>
       </c>
       <c r="AJ12">
-        <v>-0.07071941347181916</v>
+        <v>0.007213850593138827</v>
       </c>
       <c r="AK12">
-        <v>-0.03635078903980529</v>
+        <v>0.03146853146853147</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="AN12">
+        <v>-2.017699115044248</v>
+      </c>
+      <c r="AO12">
+        <v>-5.284552845528455</v>
+      </c>
+      <c r="AP12">
+        <v>-0.3982300884955752</v>
+      </c>
+      <c r="AQ12">
+        <v>-5.284552845528455</v>
       </c>
     </row>
     <row r="13">
@@ -1939,7 +1930,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Somerley Capital Holdings Limited (SEHK:8439)</t>
+          <t>Goldstone Investment Group Limited (SEHK:901)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1947,119 +1938,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.0203</v>
-      </c>
-      <c r="G13">
-        <v>0.002233502538071066</v>
-      </c>
-      <c r="H13">
-        <v>0.002233502538071066</v>
-      </c>
-      <c r="I13">
-        <v>0.001725888324873097</v>
-      </c>
-      <c r="J13">
-        <v>0.001725888324873097</v>
-      </c>
       <c r="K13">
-        <v>0.281</v>
-      </c>
-      <c r="L13">
-        <v>0.02852791878172589</v>
+        <v>-4.36</v>
       </c>
       <c r="M13">
-        <v>0.6929999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.02717647058823529</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>2.466192170818505</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>0.6929999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.02717647058823529</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>2.466192170818505</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>10.6</v>
+        <v>0.419</v>
       </c>
       <c r="V13">
-        <v>0.4156862745098039</v>
+        <v>0.02950704225352113</v>
       </c>
       <c r="W13">
-        <v>0.02128787878787879</v>
+        <v>1.018691588785047</v>
       </c>
       <c r="X13">
-        <v>0.05084765712860254</v>
+        <v>0.1306570475127204</v>
       </c>
       <c r="Y13">
-        <v>-0.02955977834072375</v>
+        <v>0.8880345412723263</v>
       </c>
       <c r="Z13">
-        <v>1.634854771784233</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.002821576763485478</v>
+        <v>-0.1416464173531678</v>
       </c>
       <c r="AB13">
-        <v>0.04902325318628185</v>
+        <v>0.08440942437509404</v>
       </c>
       <c r="AC13">
-        <v>-0.04620167642279637</v>
+        <v>-0.2260558417282618</v>
       </c>
       <c r="AD13">
-        <v>2.47</v>
+        <v>22.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.47</v>
+        <v>22.5</v>
       </c>
       <c r="AG13">
-        <v>-8.129999999999999</v>
+        <v>22.081</v>
       </c>
       <c r="AH13">
-        <v>0.08830890239542367</v>
+        <v>0.6130790190735694</v>
       </c>
       <c r="AI13">
-        <v>0.1617550753110674</v>
+        <v>1.573426573426573</v>
       </c>
       <c r="AJ13">
-        <v>-0.468048359240069</v>
+        <v>0.6086105675146771</v>
       </c>
       <c r="AK13">
-        <v>-1.740899357601712</v>
+        <v>1.590735537785462</v>
       </c>
       <c r="AL13">
-        <v>0.032</v>
+        <v>1.95</v>
       </c>
       <c r="AM13">
-        <v>0.032</v>
-      </c>
-      <c r="AN13">
-        <v>16.46666666666667</v>
+        <v>1.95</v>
       </c>
       <c r="AO13">
-        <v>0.53125</v>
-      </c>
-      <c r="AP13">
-        <v>-54.2</v>
+        <v>-1.225641025641026</v>
       </c>
       <c r="AQ13">
-        <v>0.53125</v>
+        <v>-1.225641025641026</v>
       </c>
     </row>
     <row r="14">
@@ -2070,7 +2034,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Goldenbridge Acquisition Limited (NasdaqCM:GBRG)</t>
+          <t>Capital VC Limited (SEHK:2324)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2079,7 +2043,7 @@
         </is>
       </c>
       <c r="K14">
-        <v>-0.946</v>
+        <v>-11.2</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2103,64 +2067,67 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.638</v>
+        <v>2.13</v>
       </c>
       <c r="V14">
-        <v>0.008495339547270307</v>
+        <v>0.301699716713881</v>
       </c>
       <c r="W14">
-        <v>6.709219858156029</v>
+        <v>-0.1651917404129793</v>
       </c>
       <c r="X14">
-        <v>0.04817639956685044</v>
+        <v>0.08774137401640666</v>
       </c>
       <c r="Y14">
-        <v>6.661043458589178</v>
+        <v>-0.252933114429386</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>-0.1629696695337257</v>
       </c>
       <c r="AB14">
-        <v>0.04817400466792005</v>
+        <v>0.08053477309947665</v>
       </c>
       <c r="AC14">
-        <v>-0.04817400466792005</v>
+        <v>-0.2435044426332023</v>
       </c>
       <c r="AD14">
-        <v>0.01</v>
+        <v>2.01</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.01</v>
+        <v>2.01</v>
       </c>
       <c r="AG14">
-        <v>-0.628</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.0001331380641725469</v>
+        <v>0.2216097023153252</v>
       </c>
       <c r="AI14">
-        <v>-0.004545454545454545</v>
+        <v>0.03257170636849781</v>
       </c>
       <c r="AJ14">
-        <v>-0.008432699538081427</v>
+        <v>-0.01729106628242076</v>
       </c>
       <c r="AK14">
-        <v>0.2212825933756166</v>
+        <v>-0.002014098690835853</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="AM14">
-        <v>-0.005</v>
+        <v>0.391</v>
+      </c>
+      <c r="AO14">
+        <v>-27.62148337595908</v>
       </c>
       <c r="AQ14">
-        <v>-0</v>
+        <v>-27.62148337595908</v>
       </c>
     </row>
     <row r="15">
@@ -2171,7 +2138,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bridgetown Holdings Limited (NasdaqCM:BTWN)</t>
+          <t>OCI International Holdings Limited (SEHK:329)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2179,8 +2146,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D15">
+        <v>0.0993</v>
+      </c>
+      <c r="G15">
+        <v>-4.188811188811189</v>
+      </c>
+      <c r="H15">
+        <v>-4.188811188811189</v>
+      </c>
+      <c r="I15">
+        <v>-9.23076923076923</v>
+      </c>
+      <c r="J15">
+        <v>-9.23076923076923</v>
+      </c>
       <c r="K15">
-        <v>-75.09999999999999</v>
+        <v>-22.3</v>
+      </c>
+      <c r="L15">
+        <v>-15.5944055944056</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2204,64 +2189,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.08</v>
+        <v>34.9</v>
       </c>
       <c r="V15">
-        <v>0.001478641840087623</v>
+        <v>0.1343858298036196</v>
       </c>
       <c r="W15">
-        <v>-3952.631578947368</v>
+        <v>-0.3468118195956454</v>
       </c>
       <c r="X15">
-        <v>0.0481840650855011</v>
+        <v>0.07920586331692614</v>
       </c>
       <c r="Y15">
-        <v>-3952.679763012454</v>
+        <v>-0.4260176829125716</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>0.01988873435326843</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>-0.1835883171070932</v>
       </c>
       <c r="AB15">
-        <v>0.04817667665602879</v>
+        <v>0.07859389322757537</v>
       </c>
       <c r="AC15">
-        <v>-0.04817667665602879</v>
+        <v>-0.2621822103346685</v>
       </c>
       <c r="AD15">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="AG15">
-        <v>-0.78</v>
+        <v>-28.1</v>
       </c>
       <c r="AH15">
-        <v>0.0004105652114410839</v>
+        <v>0.02551594746716698</v>
       </c>
       <c r="AI15">
-        <v>-0.005660377358490566</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="AJ15">
-        <v>-0.001069049642279543</v>
+        <v>-0.1213298791018998</v>
       </c>
       <c r="AK15">
-        <v>0.01442307692307692</v>
+        <v>-2.14503816793893</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>0.916</v>
       </c>
       <c r="AM15">
-        <v>-0.479</v>
+        <v>0.907</v>
+      </c>
+      <c r="AN15">
+        <v>-0.5190839694656488</v>
+      </c>
+      <c r="AO15">
+        <v>-14.41048034934498</v>
+      </c>
+      <c r="AP15">
+        <v>2.145038167938931</v>
       </c>
       <c r="AQ15">
-        <v>-0</v>
+        <v>-14.55347298787211</v>
       </c>
     </row>
     <row r="16">
@@ -2272,7 +2266,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AGBA Acquisition Limited (NasdaqCM:AGBA)</t>
+          <t>China Financial International Investments Limited (SEHK:721)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2281,7 +2275,7 @@
         </is>
       </c>
       <c r="K16">
-        <v>-1.14</v>
+        <v>-27.4</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2305,64 +2299,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.356</v>
+        <v>5.05</v>
       </c>
       <c r="V16">
-        <v>0.006054421768707483</v>
+        <v>0.09960552268244575</v>
       </c>
       <c r="W16">
-        <v>-0.228</v>
+        <v>-0.2660194174757282</v>
       </c>
       <c r="X16">
-        <v>0.05008421885889023</v>
+        <v>0.07920747068752179</v>
       </c>
       <c r="Y16">
-        <v>-0.2780842188588902</v>
+        <v>-0.34522688816325</v>
       </c>
       <c r="Z16">
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>-0.2633813143981785</v>
       </c>
       <c r="AB16">
-        <v>0.04838191397375902</v>
+        <v>0.07859435078107756</v>
       </c>
       <c r="AC16">
-        <v>-0.04838191397375902</v>
+        <v>-0.3419756651792561</v>
       </c>
       <c r="AD16">
-        <v>4.07</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>4.07</v>
+        <v>1.33</v>
       </c>
       <c r="AG16">
-        <v>3.714</v>
+        <v>-3.72</v>
       </c>
       <c r="AH16">
-        <v>0.06473675839032926</v>
+        <v>0.02556217566788391</v>
       </c>
       <c r="AI16">
-        <v>2.325714285714285</v>
+        <v>0.01789317906632585</v>
       </c>
       <c r="AJ16">
-        <v>0.05941069200499089</v>
+        <v>-0.07918263090676883</v>
       </c>
       <c r="AK16">
-        <v>2.664275466284074</v>
+        <v>-0.05369515011547343</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AM16">
-        <v>-0.025</v>
+        <v>0.095</v>
+      </c>
+      <c r="AN16">
+        <v>-0.04889705882352942</v>
+      </c>
+      <c r="AO16">
+        <v>-287.3684210526316</v>
+      </c>
+      <c r="AP16">
+        <v>0.1367647058823529</v>
       </c>
       <c r="AQ16">
-        <v>-0</v>
+        <v>-287.3684210526316</v>
       </c>
     </row>
     <row r="17">
@@ -2373,7 +2376,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>China Vered Financial Holding Corporation Limited (SEHK:245)</t>
+          <t>Cocoon Holdings Limited (SEHK:428)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2381,26 +2384,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.156</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
       <c r="K17">
-        <v>66</v>
-      </c>
-      <c r="L17">
-        <v>2.05607476635514</v>
+        <v>-7.56</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2409,7 +2394,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2418,67 +2403,79 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>65.5</v>
+        <v>0.027</v>
       </c>
       <c r="V17">
-        <v>0.2195776064364733</v>
+        <v>0.0006553398058252427</v>
       </c>
       <c r="W17">
-        <v>0.09697325888921539</v>
+        <v>-0.336</v>
       </c>
       <c r="X17">
-        <v>0.05045937461133</v>
+        <v>0.08020055462720378</v>
       </c>
       <c r="Y17">
-        <v>0.04651388427788539</v>
+        <v>-0.4162005546272037</v>
       </c>
       <c r="Z17">
-        <v>0.04934286373068941</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>-0.2907527221082531</v>
       </c>
       <c r="AB17">
-        <v>0.04871469248354397</v>
+        <v>0.07886897916171554</v>
       </c>
       <c r="AC17">
-        <v>-0.04871469248354397</v>
+        <v>-0.3696217012699687</v>
       </c>
       <c r="AD17">
-        <v>24.7</v>
+        <v>2.32</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>24.7</v>
+        <v>2.32</v>
       </c>
       <c r="AG17">
-        <v>-40.8</v>
+        <v>2.293</v>
       </c>
       <c r="AH17">
-        <v>0.07647058823529411</v>
+        <v>0.05330882352941176</v>
       </c>
       <c r="AI17">
-        <v>0.03543250609668627</v>
+        <v>0.1412911084043849</v>
       </c>
       <c r="AJ17">
-        <v>-0.1584466019417476</v>
+        <v>0.05272112753776469</v>
       </c>
       <c r="AK17">
-        <v>-0.06459784673844204</v>
+        <v>0.1398767766729702</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>0.19</v>
+      </c>
+      <c r="AN17">
+        <v>-0.3147896879240162</v>
+      </c>
+      <c r="AO17">
+        <v>-38.78947368421053</v>
+      </c>
+      <c r="AP17">
+        <v>-0.3111261872455902</v>
+      </c>
+      <c r="AQ17">
+        <v>-38.78947368421053</v>
       </c>
     </row>
     <row r="18">
@@ -2489,7 +2486,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Central Wealth Group Holdings Limited (SEHK:139)</t>
+          <t>China Internet Investment Finance Holdings Limited (SEHK:810)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2497,23 +2494,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.314</v>
+      </c>
       <c r="G18">
-        <v>0</v>
+        <v>-32.43243243243244</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>-32.43243243243244</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-27.97297297297297</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>-27.97297297297297</v>
       </c>
       <c r="K18">
-        <v>-15</v>
+        <v>-2.31</v>
       </c>
       <c r="L18">
-        <v>-0.303030303030303</v>
+        <v>-31.21621621621622</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2537,61 +2537,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>10.7</v>
+        <v>2.07</v>
       </c>
       <c r="V18">
-        <v>0.5219512195121951</v>
+        <v>0.004856874706710464</v>
       </c>
       <c r="W18">
-        <v>-0.08818342151675486</v>
+        <v>-0.21</v>
       </c>
       <c r="X18">
-        <v>0.1528430487744152</v>
+        <v>0.07835505558371328</v>
       </c>
       <c r="Y18">
-        <v>-0.24102647029117</v>
+        <v>-0.2883550555837133</v>
       </c>
       <c r="Z18">
-        <v>0.1870748299319728</v>
+        <v>0.01125304136253041</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>-0.3147810218978102</v>
       </c>
       <c r="AB18">
-        <v>0.05378049550944723</v>
+        <v>0.07834545247532355</v>
       </c>
       <c r="AC18">
-        <v>-0.05378049550944723</v>
+        <v>-0.3931264743731337</v>
       </c>
       <c r="AD18">
-        <v>77.7</v>
+        <v>0.177</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>77.7</v>
+        <v>0.177</v>
       </c>
       <c r="AG18">
-        <v>67</v>
+        <v>-1.893</v>
       </c>
       <c r="AH18">
-        <v>0.7912423625254582</v>
+        <v>0.0004151255813517145</v>
       </c>
       <c r="AI18">
-        <v>0.3441098317094774</v>
+        <v>0.02028188380886902</v>
       </c>
       <c r="AJ18">
-        <v>0.7657142857142857</v>
+        <v>-0.004461392340922963</v>
       </c>
       <c r="AK18">
-        <v>0.3114830311483031</v>
+        <v>-0.284362325371789</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>0.005</v>
+      </c>
+      <c r="AN18">
+        <v>-0.08984771573604061</v>
+      </c>
+      <c r="AO18">
+        <v>-413.9999999999999</v>
+      </c>
+      <c r="AP18">
+        <v>0.9609137055837562</v>
+      </c>
+      <c r="AQ18">
+        <v>-413.9999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2602,7 +2614,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CST Group Limited (SEHK:985)</t>
+          <t>DT Capital Limited (SEHK:356)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2610,26 +2622,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D19">
-        <v>0.0501</v>
-      </c>
-      <c r="G19">
-        <v>0.2794759825327511</v>
-      </c>
-      <c r="H19">
-        <v>0.2794759825327511</v>
-      </c>
-      <c r="I19">
-        <v>-0.1037117903930131</v>
-      </c>
-      <c r="J19">
-        <v>-0.1037117903930131</v>
-      </c>
       <c r="K19">
-        <v>-215.4</v>
-      </c>
-      <c r="L19">
-        <v>-4.703056768558953</v>
+        <v>-3.5</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2653,73 +2647,61 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>48.7</v>
+        <v>0.326</v>
       </c>
       <c r="V19">
-        <v>0.3244503664223851</v>
+        <v>0.0163</v>
       </c>
       <c r="W19">
-        <v>-0.4171993027309704</v>
+        <v>-0.2348993288590604</v>
       </c>
       <c r="X19">
-        <v>0.1356562425127324</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y19">
-        <v>-0.5528555452437027</v>
+        <v>-0.3132406725401708</v>
       </c>
       <c r="Z19">
-        <v>0.04639384116693679</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>-0.004811588330632091</v>
+        <v>-0.3210484651244613</v>
       </c>
       <c r="AB19">
-        <v>0.05355956993599337</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC19">
-        <v>-0.05837115826662546</v>
+        <v>-0.3993898088055717</v>
       </c>
       <c r="AD19">
-        <v>475.5</v>
+        <v>0</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>475.5</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>426.8</v>
+        <v>-0.326</v>
       </c>
       <c r="AH19">
-        <v>0.7600703324808183</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>0.6298013245033113</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>0.7398162593170394</v>
+        <v>-0.01657009250787842</v>
       </c>
       <c r="AK19">
-        <v>0.6042758034829393</v>
+        <v>-0.02512717743178665</v>
       </c>
       <c r="AL19">
-        <v>6.96</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>6.811</v>
-      </c>
-      <c r="AN19">
-        <v>34.96323529411764</v>
-      </c>
-      <c r="AO19">
-        <v>-0.6824712643678161</v>
-      </c>
-      <c r="AP19">
-        <v>31.38235294117647</v>
-      </c>
-      <c r="AQ19">
-        <v>-0.6974012626633387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2730,7 +2712,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>China Innovation Investment Limited (SEHK:1217)</t>
+          <t>China Investment Development Limited (SEHK:204)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2738,23 +2720,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.472</v>
+      </c>
       <c r="G20">
-        <v>-0</v>
+        <v>-3.078260869565218</v>
       </c>
       <c r="H20">
-        <v>-0</v>
+        <v>-3.078260869565218</v>
       </c>
       <c r="I20">
-        <v>2.273603082851638</v>
+        <v>-6.286956521739131</v>
       </c>
       <c r="J20">
-        <v>2.273603082851638</v>
+        <v>-6.286956521739131</v>
       </c>
       <c r="K20">
-        <v>2.47</v>
+        <v>-5.65</v>
       </c>
       <c r="L20">
-        <v>-4.759152215799615</v>
+        <v>-4.91304347826087</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2763,7 +2748,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2772,73 +2757,79 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1.7</v>
+        <v>0.555</v>
       </c>
       <c r="V20">
-        <v>0.1036585365853659</v>
+        <v>0.02032967032967033</v>
       </c>
       <c r="W20">
-        <v>0.02810011376564278</v>
+        <v>-0.2344398340248963</v>
       </c>
       <c r="X20">
-        <v>0.04856338382323901</v>
+        <v>0.08148582196432252</v>
       </c>
       <c r="Y20">
-        <v>-0.02046327005759624</v>
+        <v>-0.3159256559892188</v>
       </c>
       <c r="Z20">
-        <v>-0.00658997409721164</v>
+        <v>0.05455407969639468</v>
       </c>
       <c r="AA20">
-        <v>-0.01498298542333282</v>
+        <v>-0.3429791271347248</v>
       </c>
       <c r="AB20">
-        <v>0.04821779748407105</v>
+        <v>0.07920201445007351</v>
       </c>
       <c r="AC20">
-        <v>-0.06320078290740387</v>
+        <v>-0.4221811415847984</v>
       </c>
       <c r="AD20">
-        <v>0.232</v>
+        <v>2.6</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.232</v>
+        <v>2.6</v>
       </c>
       <c r="AG20">
-        <v>-1.468</v>
+        <v>2.045</v>
       </c>
       <c r="AH20">
-        <v>0.01394901394901395</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="AI20">
-        <v>0.002706107404469743</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AJ20">
-        <v>-0.0983123493169033</v>
+        <v>0.06968819219628557</v>
       </c>
       <c r="AK20">
-        <v>-0.01746953541507997</v>
+        <v>0.07291852380103404</v>
       </c>
       <c r="AL20">
-        <v>0.008</v>
+        <v>0.347</v>
       </c>
       <c r="AM20">
-        <v>0.008</v>
+        <v>0.347</v>
+      </c>
+      <c r="AN20">
+        <v>-0.359612724757953</v>
       </c>
       <c r="AO20">
-        <v>-147.5</v>
+        <v>-20.835734870317</v>
+      </c>
+      <c r="AP20">
+        <v>-0.2828492392807745</v>
       </c>
       <c r="AQ20">
-        <v>-147.5</v>
+        <v>-20.835734870317</v>
       </c>
     </row>
     <row r="21">
@@ -2849,7 +2840,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Harbour Digital Asset Capital Limited (SEHK:913)</t>
+          <t>Core Economy Investment Group Limited (SEHK:339)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2857,23 +2848,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D21">
+        <v>-0.247</v>
+      </c>
       <c r="G21">
-        <v>0</v>
+        <v>-31.42857142857143</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>-31.42857142857143</v>
       </c>
       <c r="I21">
-        <v>-1.414486921529175</v>
+        <v>-28.28571428571428</v>
       </c>
       <c r="J21">
-        <v>-1.414486921529175</v>
+        <v>-28.28571428571428</v>
       </c>
       <c r="K21">
-        <v>-1.02</v>
+        <v>-2.33</v>
       </c>
       <c r="L21">
-        <v>-2.052313883299799</v>
+        <v>-66.57142857142857</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2897,67 +2891,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>1.74</v>
+        <v>0.188</v>
       </c>
       <c r="V21">
-        <v>0.05594855305466238</v>
+        <v>0.04486873508353222</v>
       </c>
       <c r="W21">
-        <v>-0.03207547169811321</v>
+        <v>-0.5796019900497513</v>
       </c>
       <c r="X21">
-        <v>0.04817272237335087</v>
+        <v>0.08178488511369245</v>
       </c>
       <c r="Y21">
-        <v>-0.08024819407146408</v>
+        <v>-0.6613868751634437</v>
       </c>
       <c r="Z21">
-        <v>0.01590196454853779</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="AA21">
-        <v>-0.02249312088052729</v>
+        <v>-0.3626373626373627</v>
       </c>
       <c r="AB21">
-        <v>0.04817272237335087</v>
+        <v>0.08184704455628308</v>
       </c>
       <c r="AC21">
-        <v>-0.07066584325387816</v>
+        <v>-0.4444844071936458</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="AG21">
-        <v>-1.74</v>
+        <v>0.249</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>0.0944456451264318</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>0.2103996148290804</v>
       </c>
       <c r="AJ21">
-        <v>-0.05926430517711171</v>
+        <v>0.05609371480063077</v>
       </c>
       <c r="AK21">
-        <v>-0.05750165234633179</v>
+        <v>0.1318157755426151</v>
       </c>
       <c r="AL21">
-        <v>0.005</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AM21">
-        <v>0.005</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AN21">
+        <v>-0.4528497409326425</v>
       </c>
       <c r="AO21">
-        <v>-140.6</v>
+        <v>-14.14285714285714</v>
+      </c>
+      <c r="AP21">
+        <v>-0.2580310880829015</v>
       </c>
       <c r="AQ21">
-        <v>-140.6</v>
+        <v>-14.14285714285714</v>
       </c>
     </row>
     <row r="22">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jade Road Investments Limited (AIM:JADE)</t>
+          <t>Somerley Capital Holdings Limited (SEHK:8439)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2976,95 +2976,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D22">
+        <v>-0.0418</v>
+      </c>
+      <c r="G22">
+        <v>-0.04537037037037037</v>
+      </c>
+      <c r="H22">
+        <v>-0.04537037037037037</v>
+      </c>
+      <c r="I22">
+        <v>-0.2288359788359788</v>
+      </c>
+      <c r="J22">
+        <v>-0.2288359788359788</v>
+      </c>
       <c r="K22">
-        <v>2.07</v>
+        <v>-1.69</v>
+      </c>
+      <c r="L22">
+        <v>-0.2235449735449735</v>
       </c>
       <c r="M22">
-        <v>0.201</v>
+        <v>0.453</v>
       </c>
       <c r="N22">
-        <v>0.01717948717948718</v>
+        <v>0.02359375</v>
       </c>
       <c r="O22">
-        <v>0.09710144927536234</v>
+        <v>-0.2680473372781065</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>0.453</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.02359375</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>-0.2680473372781065</v>
       </c>
       <c r="S22">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.56</v>
+        <v>8.4</v>
       </c>
       <c r="V22">
-        <v>0.2188034188034188</v>
+        <v>0.4375000000000001</v>
       </c>
       <c r="W22">
-        <v>0.02065868263473054</v>
+        <v>-0.1330708661417323</v>
       </c>
       <c r="X22">
-        <v>0.05652824887449513</v>
+        <v>0.08097238761964179</v>
       </c>
       <c r="Y22">
-        <v>-0.0358695662397646</v>
+        <v>-0.2140432537613741</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.654266958424508</v>
       </c>
       <c r="AA22">
-        <v>-0.05006456739843052</v>
+        <v>-0.3785557986870897</v>
       </c>
       <c r="AB22">
-        <v>0.04981898530649344</v>
+        <v>0.07907185512249514</v>
       </c>
       <c r="AC22">
-        <v>-0.09988355270492395</v>
+        <v>-0.4576276538095848</v>
       </c>
       <c r="AD22">
-        <v>3.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>3.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG22">
-        <v>0.98</v>
+        <v>-6.87</v>
       </c>
       <c r="AH22">
-        <v>0.2322834645669292</v>
+        <v>0.07380607814761216</v>
       </c>
       <c r="AI22">
-        <v>0.03225806451612903</v>
+        <v>0.1271820448877806</v>
       </c>
       <c r="AJ22">
-        <v>0.07728706624605679</v>
+        <v>-0.5571776155717763</v>
       </c>
       <c r="AK22">
-        <v>0.009143496921067362</v>
+        <v>-1.892561983471075</v>
       </c>
       <c r="AL22">
-        <v>0.522</v>
+        <v>0.048</v>
       </c>
       <c r="AM22">
-        <v>-0.8180000000000001</v>
+        <v>0.048</v>
+      </c>
+      <c r="AN22">
+        <v>-0.9444444444444444</v>
       </c>
       <c r="AO22">
-        <v>-9.655172413793103</v>
+        <v>-36.04166666666666</v>
+      </c>
+      <c r="AP22">
+        <v>4.24074074074074</v>
       </c>
       <c r="AQ22">
-        <v>6.161369193154034</v>
+        <v>-36.04166666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3075,7 +3099,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Global Mastermind Capital Limited (SEHK:905)</t>
+          <t>AP Acquisition Corp. (NYSE:APCA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3083,26 +3107,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D23">
-        <v>-0.137</v>
-      </c>
-      <c r="G23">
-        <v>-2.534246575342466</v>
-      </c>
-      <c r="H23">
-        <v>-2.534246575342466</v>
-      </c>
-      <c r="I23">
-        <v>-3.373287671232877</v>
-      </c>
-      <c r="J23">
-        <v>-3.373287671232877</v>
-      </c>
       <c r="K23">
-        <v>8.15</v>
-      </c>
-      <c r="L23">
-        <v>13.9554794520548</v>
+        <v>0.049</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3126,73 +3132,64 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0.284</v>
+        <v>0.366</v>
       </c>
       <c r="V23">
-        <v>0.02028571428571429</v>
+        <v>0.001644943820224719</v>
       </c>
       <c r="W23">
-        <v>0.2523219814241486</v>
+        <v>-49</v>
       </c>
       <c r="X23">
-        <v>0.05823273581813049</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y23">
-        <v>0.1940892456060181</v>
+        <v>-49.07834134368111</v>
       </c>
       <c r="Z23">
-        <v>0.01725666331777082</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>-0.05821168961645293</v>
+        <v>-8.14516129032258</v>
       </c>
       <c r="AB23">
-        <v>0.05074443462449368</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC23">
-        <v>-0.1089561242409466</v>
+        <v>-8.22350263400369</v>
       </c>
       <c r="AD23">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>4.816</v>
+        <v>-0.366</v>
       </c>
       <c r="AH23">
-        <v>0.2670157068062827</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.1120879120879121</v>
+        <v>-0</v>
       </c>
       <c r="AJ23">
-        <v>0.2559523809523809</v>
+        <v>-0.001647654118685118</v>
       </c>
       <c r="AK23">
-        <v>0.1065109695682944</v>
+        <v>0.06023699802501646</v>
       </c>
       <c r="AL23">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>0.125</v>
-      </c>
-      <c r="AN23">
-        <v>-2.865168539325842</v>
-      </c>
-      <c r="AO23">
-        <v>-15.76</v>
-      </c>
-      <c r="AP23">
-        <v>-2.70561797752809</v>
+        <v>-1.06</v>
       </c>
       <c r="AQ23">
-        <v>-15.76</v>
+        <v>0.9528301886792453</v>
       </c>
     </row>
     <row r="24">
@@ -3203,7 +3200,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alberton Acquisition Corporation (NasdaqCM:ALAC)</t>
+          <t>True Partner Capital Holding Limited (SEHK:8657)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3211,17 +3208,32 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G24">
+        <v>-0.4042553191489362</v>
+      </c>
+      <c r="H24">
+        <v>-0.4042553191489362</v>
+      </c>
+      <c r="I24">
+        <v>-0.5617719871774672</v>
+      </c>
+      <c r="J24">
+        <v>-0.5617719871774672</v>
+      </c>
       <c r="K24">
-        <v>-0.611</v>
+        <v>-3.9</v>
+      </c>
+      <c r="L24">
+        <v>-0.5927051671732523</v>
       </c>
       <c r="M24">
-        <v>1.51</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.02881679389312977</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>-2.471358428805237</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3233,70 +3245,70 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>1.51</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.908396946564886e-05</v>
-      </c>
-      <c r="W24">
-        <v>-0.1222</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>0.05049687006860867</v>
-      </c>
-      <c r="Y24">
-        <v>-0.1726968700686087</v>
+        <v>0.07874794384476688</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>241.0399609300854</v>
       </c>
       <c r="AA24">
-        <v>-0.0869401107196779</v>
+        <v>-135.4094978408731</v>
       </c>
       <c r="AB24">
-        <v>0.04842356832347852</v>
+        <v>0.07842315018723649</v>
       </c>
       <c r="AC24">
-        <v>-0.1353636790431564</v>
+        <v>-135.4879209910604</v>
       </c>
       <c r="AD24">
-        <v>4.41</v>
+        <v>0.485</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>0.02729837813867119</v>
       </c>
       <c r="AF24">
-        <v>4.41</v>
+        <v>0.5122983781386712</v>
       </c>
       <c r="AG24">
-        <v>4.409</v>
+        <v>0.5122983781386712</v>
       </c>
       <c r="AH24">
-        <v>0.07762717831367717</v>
+        <v>0.01216505386475451</v>
       </c>
       <c r="AI24">
-        <v>-0.8981670061099797</v>
+        <v>0.02178852827994891</v>
       </c>
       <c r="AJ24">
-        <v>0.0776109419282156</v>
+        <v>0.01216505386475451</v>
       </c>
       <c r="AK24">
-        <v>-0.8977804927713295</v>
+        <v>0.02178852827994891</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AM24">
-        <v>-0.001</v>
+        <v>0.014</v>
+      </c>
+      <c r="AN24">
+        <v>-0.1401329095637099</v>
+      </c>
+      <c r="AO24">
+        <v>-265.7142857142857</v>
+      </c>
+      <c r="AP24">
+        <v>-0.1480203346254467</v>
       </c>
       <c r="AQ24">
-        <v>690.9999999999999</v>
+        <v>-265.7142857142857</v>
       </c>
     </row>
     <row r="25">
@@ -3307,7 +3319,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>China Financial International Investments Limited (SEHK:721)</t>
+          <t>HH&amp;L Acquisition Co. (NYSE:HHLA)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3315,23 +3327,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G25">
-        <v>1.367911479944675</v>
-      </c>
-      <c r="H25">
-        <v>1.367911479944675</v>
-      </c>
-      <c r="I25">
-        <v>1.369294605809129</v>
-      </c>
-      <c r="J25">
-        <v>1.369294605809129</v>
-      </c>
       <c r="K25">
-        <v>-8.58</v>
-      </c>
-      <c r="L25">
-        <v>1.186721991701245</v>
+        <v>12.2</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3340,7 +3337,7 @@
         <v>-0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3349,79 +3346,61 @@
         <v>-0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0.778</v>
+        <v>0.293</v>
       </c>
       <c r="V25">
-        <v>0.005421602787456447</v>
+        <v>0.0005600152905198775</v>
       </c>
       <c r="W25">
-        <v>-0.08155893536121672</v>
+        <v>-0.431095406360424</v>
       </c>
       <c r="X25">
-        <v>0.04844791738484843</v>
+        <v>0.07837289664553485</v>
       </c>
       <c r="Y25">
-        <v>-0.1300068527460652</v>
-      </c>
-      <c r="Z25">
-        <v>-0.0686023341873043</v>
-      </c>
-      <c r="AA25">
-        <v>-0.09393680614859094</v>
+        <v>-0.5094683030059588</v>
       </c>
       <c r="AB25">
-        <v>0.04824265158787244</v>
-      </c>
-      <c r="AC25">
-        <v>-0.1421794577364634</v>
+        <v>0.07835079347473566</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>0.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.43</v>
+        <v>0.5</v>
       </c>
       <c r="AG25">
-        <v>0.6519999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="AH25">
-        <v>0.009866832263851514</v>
+        <v>0.0009547450830628221</v>
       </c>
       <c r="AI25">
-        <v>0.0136933831274538</v>
+        <v>-0.02762430939226519</v>
       </c>
       <c r="AJ25">
-        <v>0.004523003496309451</v>
+        <v>0.0003954857309894594</v>
       </c>
       <c r="AK25">
-        <v>0.006290279010535252</v>
+        <v>-0.01125428152014353</v>
       </c>
       <c r="AL25">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>0.219</v>
-      </c>
-      <c r="AN25">
-        <v>-0.1445904954499494</v>
-      </c>
-      <c r="AO25">
-        <v>-45.2054794520548</v>
-      </c>
-      <c r="AP25">
-        <v>-0.06592517694641051</v>
+        <v>-2.5</v>
       </c>
       <c r="AQ25">
-        <v>-45.2054794520548</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="26">
@@ -3432,7 +3411,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DT Capital Limited (SEHK:356)</t>
+          <t>Primavera Capital Acquisition Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3440,26 +3419,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D26">
-        <v>-0.363</v>
-      </c>
-      <c r="G26">
-        <v>-8.648208469055374</v>
-      </c>
-      <c r="H26">
-        <v>-8.648208469055374</v>
-      </c>
-      <c r="I26">
-        <v>-1.824104234527687</v>
-      </c>
-      <c r="J26">
-        <v>-1.824104234527687</v>
-      </c>
       <c r="K26">
-        <v>-1.32</v>
-      </c>
-      <c r="L26">
-        <v>-2.149837133550489</v>
+        <v>18</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3468,7 +3429,7 @@
         <v>-0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3477,79 +3438,61 @@
         <v>-0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
       <c r="U26">
-        <v>3.57</v>
+        <v>0.059</v>
       </c>
       <c r="V26">
-        <v>0.2428571428571429</v>
+        <v>0.000120359037127703</v>
       </c>
       <c r="W26">
-        <v>-0.08098159509202454</v>
+        <v>-0.4455445544554456</v>
       </c>
       <c r="X26">
-        <v>0.04824598857771061</v>
+        <v>0.07837071010620331</v>
       </c>
       <c r="Y26">
-        <v>-0.1292275836697352</v>
-      </c>
-      <c r="Z26">
-        <v>0.05424507465323791</v>
-      </c>
-      <c r="AA26">
-        <v>-0.0989486703772418</v>
+        <v>-0.5239152645616488</v>
       </c>
       <c r="AB26">
-        <v>0.04819147566436102</v>
-      </c>
-      <c r="AC26">
-        <v>-0.1471401460416028</v>
+        <v>0.07834160602067695</v>
       </c>
       <c r="AD26">
-        <v>0.039</v>
+        <v>0.436</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0.039</v>
+        <v>0.436</v>
       </c>
       <c r="AG26">
-        <v>-3.531</v>
+        <v>0.377</v>
       </c>
       <c r="AH26">
-        <v>0.002646041115408101</v>
+        <v>0.0008886424966777815</v>
       </c>
       <c r="AI26">
-        <v>0.002610616507128991</v>
+        <v>-0.01782210595160235</v>
       </c>
       <c r="AJ26">
-        <v>-0.3161428955143701</v>
+        <v>0.0007684828273645116</v>
       </c>
       <c r="AK26">
-        <v>-0.3105814055765678</v>
+        <v>-0.01537332300289524</v>
       </c>
       <c r="AL26">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>0.015</v>
-      </c>
-      <c r="AN26">
-        <v>-0.03482142857142857</v>
-      </c>
-      <c r="AO26">
-        <v>-74.66666666666667</v>
-      </c>
-      <c r="AP26">
-        <v>3.152678571428571</v>
+        <v>-2.5</v>
       </c>
       <c r="AQ26">
-        <v>-74.66666666666667</v>
+        <v>2.656</v>
       </c>
     </row>
     <row r="27">
@@ -3560,7 +3503,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>China Development Bank International Investment Limited (SEHK:1062)</t>
+          <t>Bridgetown Holdings Limited (NasdaqCM:BTWN)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3568,23 +3511,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G27">
-        <v>-0</v>
-      </c>
-      <c r="H27">
-        <v>-0</v>
-      </c>
-      <c r="I27">
-        <v>1.066852367688022</v>
-      </c>
-      <c r="J27">
-        <v>1.066852367688022</v>
-      </c>
       <c r="K27">
-        <v>-34.2</v>
-      </c>
-      <c r="L27">
-        <v>0.9526462395543177</v>
+        <v>32.1</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3593,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3602,73 +3530,61 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>35</v>
+        <v>0.22</v>
       </c>
       <c r="V27">
-        <v>0.7352941176470588</v>
+        <v>0.0007407407407407407</v>
       </c>
       <c r="W27">
-        <v>-0.1333853354134166</v>
+        <v>-0.602251407129456</v>
       </c>
       <c r="X27">
-        <v>0.07729686740956407</v>
+        <v>0.07858813758273221</v>
       </c>
       <c r="Y27">
-        <v>-0.2106822028229806</v>
-      </c>
-      <c r="Z27">
-        <v>-0.1098531211750306</v>
-      </c>
-      <c r="AA27">
-        <v>-0.1171970624235006</v>
+        <v>-0.6808395447121882</v>
       </c>
       <c r="AB27">
-        <v>0.05181058057721109</v>
-      </c>
-      <c r="AC27">
-        <v>-0.1690076430007117</v>
+        <v>0.07834353395826979</v>
       </c>
       <c r="AD27">
-        <v>50.2</v>
+        <v>2.22</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>50.2</v>
+        <v>2.22</v>
       </c>
       <c r="AG27">
-        <v>15.2</v>
+        <v>2</v>
       </c>
       <c r="AH27">
-        <v>0.5132924335378323</v>
+        <v>0.007419290154401444</v>
       </c>
       <c r="AI27">
-        <v>0.184966838614591</v>
+        <v>-0.09536082474226805</v>
       </c>
       <c r="AJ27">
-        <v>0.2420382165605096</v>
+        <v>0.006688963210702341</v>
       </c>
       <c r="AK27">
-        <v>0.0642978003384095</v>
+        <v>-0.0851063829787234</v>
       </c>
       <c r="AL27">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>0.7790000000000001</v>
-      </c>
-      <c r="AO27">
-        <v>-35.13761467889908</v>
+        <v>-3.9</v>
       </c>
       <c r="AQ27">
-        <v>-49.16559691912708</v>
+        <v>0.3948717948717949</v>
       </c>
     </row>
     <row r="28">
@@ -3679,7 +3595,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Asia-Pac Financial Investment Company Limited (SEHK:8193)</t>
+          <t>Summit Healthcare Acquisition Corp. (NasdaqCM:SMIH)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3687,26 +3603,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D28">
-        <v>-0.0872</v>
-      </c>
-      <c r="G28">
-        <v>-0.7112526539278132</v>
-      </c>
-      <c r="H28">
-        <v>-0.7112526539278132</v>
-      </c>
-      <c r="I28">
-        <v>-0.8450106157112527</v>
-      </c>
-      <c r="J28">
-        <v>-0.8450106157112527</v>
-      </c>
       <c r="K28">
-        <v>-0.508</v>
-      </c>
-      <c r="L28">
-        <v>-0.1078556263269639</v>
+        <v>17.7</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3715,7 +3613,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3724,79 +3622,61 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.405</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V28">
-        <v>0.03857142857142858</v>
+        <v>0.0002712127082526153</v>
       </c>
       <c r="W28">
-        <v>-0.0319496855345912</v>
+        <v>-0.7901785714285714</v>
       </c>
       <c r="X28">
-        <v>0.06192798258673582</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y28">
-        <v>-0.09387766812132702</v>
-      </c>
-      <c r="Z28">
-        <v>0.2437383564479404</v>
-      </c>
-      <c r="AA28">
-        <v>-0.2059614986545229</v>
+        <v>-0.8685199151096819</v>
       </c>
       <c r="AB28">
-        <v>0.0513749966825067</v>
-      </c>
-      <c r="AC28">
-        <v>-0.2573364953370296</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AD28">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>4.825</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AH28">
-        <v>0.3324856961220598</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>0.1927755252488021</v>
+        <v>-0</v>
       </c>
       <c r="AJ28">
-        <v>0.3148450244698206</v>
+        <v>-0.0002712862845405573</v>
       </c>
       <c r="AK28">
-        <v>0.1805425631431244</v>
+        <v>0.01158940397350993</v>
       </c>
       <c r="AL28">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>0.225</v>
-      </c>
-      <c r="AN28">
-        <v>-1.320707070707071</v>
-      </c>
-      <c r="AO28">
-        <v>-16.65271966527197</v>
-      </c>
-      <c r="AP28">
-        <v>-1.218434343434343</v>
+        <v>-1.2</v>
       </c>
       <c r="AQ28">
-        <v>-17.68888888888889</v>
+        <v>1.275</v>
       </c>
     </row>
     <row r="29">
@@ -3807,7 +3687,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Core Economy Investment Group Limited (SEHK:339)</t>
+          <t>Magnum Opus Acquisition Limited (NYSE:OPA)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3815,23 +3695,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G29">
-        <v>-1.825525040387722</v>
-      </c>
-      <c r="H29">
-        <v>-1.825525040387722</v>
-      </c>
-      <c r="I29">
-        <v>-1.101777059773829</v>
-      </c>
-      <c r="J29">
-        <v>-1.101777059773829</v>
-      </c>
       <c r="K29">
-        <v>-0.721</v>
-      </c>
-      <c r="L29">
-        <v>-1.164781906300485</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3840,7 +3705,7 @@
         <v>-0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P29">
         <v>-0</v>
@@ -3849,79 +3714,61 @@
         <v>-0</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1.68</v>
+        <v>0.025</v>
       </c>
       <c r="V29">
-        <v>0.1555555555555555</v>
+        <v>9.920634920634921e-05</v>
       </c>
       <c r="W29">
-        <v>-0.1907407407407407</v>
+        <v>-0.3882113821138212</v>
       </c>
       <c r="X29">
-        <v>0.04916995682158066</v>
+        <v>0.07836649950737611</v>
       </c>
       <c r="Y29">
-        <v>-0.2399106975623214</v>
-      </c>
-      <c r="Z29">
-        <v>0.1994201030927835</v>
-      </c>
-      <c r="AA29">
-        <v>-0.2197164948453608</v>
+        <v>-0.4665778816211973</v>
       </c>
       <c r="AB29">
-        <v>0.04850839821415345</v>
-      </c>
-      <c r="AC29">
-        <v>-0.2682248930595142</v>
+        <v>0.07834887905518202</v>
       </c>
       <c r="AD29">
-        <v>0.39</v>
+        <v>0.192</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0.39</v>
+        <v>0.192</v>
       </c>
       <c r="AG29">
-        <v>-1.29</v>
+        <v>0.167</v>
       </c>
       <c r="AH29">
-        <v>0.03485254691689008</v>
+        <v>0.0007613247049866769</v>
       </c>
       <c r="AI29">
-        <v>0.08843537414965988</v>
+        <v>-0.01351351351351351</v>
       </c>
       <c r="AJ29">
-        <v>-0.1356466876971609</v>
+        <v>0.0006622595343562005</v>
       </c>
       <c r="AK29">
-        <v>-0.4725274725274726</v>
+        <v>-0.01173329586172978</v>
       </c>
       <c r="AL29">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>0.039</v>
-      </c>
-      <c r="AN29">
-        <v>-0.5972434915773354</v>
-      </c>
-      <c r="AO29">
-        <v>-17.48717948717949</v>
-      </c>
-      <c r="AP29">
-        <v>1.975497702909648</v>
+        <v>-1.17</v>
       </c>
       <c r="AQ29">
-        <v>-17.48717948717949</v>
+        <v>6.700854700854701</v>
       </c>
     </row>
     <row r="30">
@@ -3932,7 +3779,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Malacca Straits Acquisition Company Limited (NasdaqCM:MLAC)</t>
+          <t>Black Spade Acquisition Co (NYSE:BSAQ)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3941,7 +3788,7 @@
         </is>
       </c>
       <c r="K30">
-        <v>-1.27</v>
+        <v>1.84</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -3950,7 +3797,7 @@
         <v>-0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -3959,70 +3806,61 @@
         <v>-0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0.036</v>
+        <v>0.074</v>
       </c>
       <c r="V30">
-        <v>0.0001961852861035422</v>
+        <v>0.0003502129673450071</v>
       </c>
       <c r="W30">
-        <v>-0.254</v>
+        <v>-0.1520661157024794</v>
       </c>
       <c r="X30">
-        <v>0.04821787069462893</v>
+        <v>0.07834165619433306</v>
       </c>
       <c r="Y30">
-        <v>-0.3022178706946289</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>-0.2438441310064547</v>
+        <v>-0.2304077718968124</v>
       </c>
       <c r="AB30">
-        <v>0.04817799672451147</v>
-      </c>
-      <c r="AC30">
-        <v>-0.2920221277309662</v>
+        <v>0.07834134647534655</v>
       </c>
       <c r="AD30">
-        <v>0.3</v>
+        <v>0.002</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.3</v>
+        <v>0.002</v>
       </c>
       <c r="AG30">
-        <v>0.264</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="AH30">
-        <v>0.001632208922742111</v>
+        <v>9.465125744195511e-06</v>
       </c>
       <c r="AI30">
-        <v>-0.03099173553719008</v>
+        <v>-0.0001980590215884334</v>
       </c>
       <c r="AJ30">
-        <v>0.001436625236716658</v>
+        <v>-0.000340863900619236</v>
       </c>
       <c r="AK30">
-        <v>-0.02717167558666118</v>
+        <v>0.007078254030672434</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-0.062</v>
+        <v>-1.01</v>
       </c>
       <c r="AQ30">
-        <v>16.45161290322581</v>
+        <v>6.455445544554455</v>
       </c>
     </row>
     <row r="31">
@@ -4033,7 +3871,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>China Internet Investment Finance Holdings Limited (SEHK:810)</t>
+          <t>Aquila Acquisition Corporation (SEHK:7836)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4041,26 +3879,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D31">
-        <v>-0.257</v>
-      </c>
-      <c r="G31">
-        <v>-24.36507936507936</v>
-      </c>
-      <c r="H31">
-        <v>-24.36507936507936</v>
-      </c>
-      <c r="I31">
-        <v>-23.33333333333333</v>
-      </c>
-      <c r="J31">
-        <v>-23.33333333333333</v>
-      </c>
       <c r="K31">
-        <v>-2.9</v>
-      </c>
-      <c r="L31">
-        <v>-23.01587301587302</v>
+        <v>-0.144</v>
       </c>
       <c r="M31">
         <v>-0</v>
@@ -4084,73 +3904,46 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>4.67</v>
+        <v>1.34</v>
       </c>
       <c r="V31">
-        <v>0.1716911764705882</v>
-      </c>
-      <c r="W31">
-        <v>-0.2265625</v>
+        <v>0.009279778393351801</v>
       </c>
       <c r="X31">
-        <v>0.04842248222271521</v>
-      </c>
-      <c r="Y31">
-        <v>-0.2749849822227152</v>
-      </c>
-      <c r="Z31">
-        <v>0.01203323464807564</v>
-      </c>
-      <c r="AA31">
-        <v>-0.2807754751217649</v>
+        <v>0.07836237945688315</v>
       </c>
       <c r="AB31">
-        <v>0.04825904837237655</v>
-      </c>
-      <c r="AC31">
-        <v>-0.3290345234941414</v>
+        <v>0.07834764568865107</v>
       </c>
       <c r="AD31">
-        <v>0.246</v>
+        <v>0.092</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0.246</v>
+        <v>0.092</v>
       </c>
       <c r="AG31">
-        <v>-4.423999999999999</v>
+        <v>-1.248</v>
       </c>
       <c r="AH31">
-        <v>0.008963054725643082</v>
+        <v>0.0006367134512637377</v>
       </c>
       <c r="AI31">
-        <v>0.02187444424684332</v>
+        <v>-0.02306920762286861</v>
       </c>
       <c r="AJ31">
-        <v>-0.194239550403934</v>
+        <v>-0.008718006035542639</v>
       </c>
       <c r="AK31">
-        <v>-0.6727493917274938</v>
+        <v>0.2342342342342342</v>
       </c>
       <c r="AL31">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>0.007</v>
-      </c>
-      <c r="AN31">
-        <v>-0.08692579505300353</v>
-      </c>
-      <c r="AO31">
-        <v>-420</v>
-      </c>
-      <c r="AP31">
-        <v>1.563250883392226</v>
-      </c>
-      <c r="AQ31">
-        <v>-420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4161,7 +3954,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>China Investment Development Limited (SEHK:204)</t>
+          <t>Blue Safari Group Acquisition Corp. (NasdaqCM:BSGA)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4169,26 +3962,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D32">
-        <v>0.202</v>
-      </c>
-      <c r="G32">
-        <v>-2.854889589905363</v>
-      </c>
-      <c r="H32">
-        <v>-2.854889589905363</v>
-      </c>
-      <c r="I32">
-        <v>-7.198535987371652</v>
-      </c>
-      <c r="J32">
-        <v>-7.198535987371652</v>
-      </c>
       <c r="K32">
-        <v>-1.21</v>
-      </c>
-      <c r="L32">
-        <v>-3.817034700315457</v>
+        <v>-4.49</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4212,73 +3987,55 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>8.800000000000001</v>
+        <v>0.359</v>
       </c>
       <c r="V32">
-        <v>0.4230769230769231</v>
+        <v>0.004573248407643312</v>
       </c>
       <c r="W32">
-        <v>-0.224907063197026</v>
+        <v>2.641176470588236</v>
       </c>
       <c r="X32">
-        <v>0.05585955831023693</v>
+        <v>0.07926245550432649</v>
       </c>
       <c r="Y32">
-        <v>-0.2807666215072629</v>
-      </c>
-      <c r="Z32">
-        <v>0.06219735761550177</v>
-      </c>
-      <c r="AA32">
-        <v>-0.4477299171146137</v>
+        <v>2.561914015083909</v>
       </c>
       <c r="AB32">
-        <v>0.0497159227750284</v>
-      </c>
-      <c r="AC32">
-        <v>-0.4974458398896421</v>
+        <v>0.07834935605335401</v>
       </c>
       <c r="AD32">
-        <v>5.78</v>
+        <v>2.19</v>
       </c>
       <c r="AE32">
-        <v>0.00967953998406623</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>5.789679539984067</v>
+        <v>2.19</v>
       </c>
       <c r="AG32">
-        <v>-3.010320460015934</v>
+        <v>1.831</v>
       </c>
       <c r="AH32">
-        <v>0.217741606523609</v>
+        <v>0.02714090965423225</v>
       </c>
       <c r="AI32">
-        <v>0.1937016264172082</v>
+        <v>-0.4171428571428571</v>
       </c>
       <c r="AJ32">
-        <v>-0.1692172393128241</v>
+        <v>0.0227931931632869</v>
       </c>
       <c r="AK32">
-        <v>-0.1427390328197565</v>
+        <v>-0.3264396505615974</v>
       </c>
       <c r="AL32">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>0.092</v>
-      </c>
-      <c r="AN32">
-        <v>-2.535087719298245</v>
-      </c>
-      <c r="AO32">
-        <v>-24.89130434782609</v>
-      </c>
-      <c r="AP32">
-        <v>1.320315991235059</v>
+        <v>-0.352</v>
       </c>
       <c r="AQ32">
-        <v>-24.89130434782609</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="33">
@@ -4289,7 +4046,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CITIC Capital Acquisition Corp. (NYSE:CCAC)</t>
+          <t>Malacca Straits Acquisition Company Limited (NasdaqCM:MLAC)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4298,16 +4055,16 @@
         </is>
       </c>
       <c r="K33">
-        <v>5.76</v>
+        <v>3.15</v>
       </c>
       <c r="M33">
-        <v>7.52</v>
+        <v>96.8</v>
       </c>
       <c r="N33">
-        <v>0.02177816391543585</v>
+        <v>2.310262529832936</v>
       </c>
       <c r="O33">
-        <v>1.305555555555556</v>
+        <v>30.73015873015873</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4319,70 +4076,61 @@
         <v>-0</v>
       </c>
       <c r="S33">
-        <v>7.52</v>
+        <v>96.8</v>
       </c>
       <c r="T33">
         <v>1</v>
       </c>
       <c r="U33">
-        <v>0.061</v>
+        <v>0.203</v>
       </c>
       <c r="V33">
-        <v>0.00017665797856936</v>
+        <v>0.004844868735083533</v>
       </c>
       <c r="W33">
-        <v>1.152</v>
+        <v>-0.3156312625250501</v>
       </c>
       <c r="X33">
-        <v>0.04817272237335087</v>
+        <v>0.08045317229422708</v>
       </c>
       <c r="Y33">
-        <v>1.103827277626649</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>-1.170984455958549</v>
+        <v>-0.3960844348192771</v>
       </c>
       <c r="AB33">
-        <v>0.04817272237335087</v>
-      </c>
-      <c r="AC33">
-        <v>-1.2191571783319</v>
+        <v>0.07835909094668785</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AG33">
-        <v>-0.061</v>
+        <v>2.477</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>0.06011664423508301</v>
       </c>
       <c r="AI33">
-        <v>-0</v>
+        <v>-0.4710017574692443</v>
       </c>
       <c r="AJ33">
-        <v>-0.0001766891921248758</v>
+        <v>0.05581720260495303</v>
       </c>
       <c r="AK33">
-        <v>0.002166116260075992</v>
+        <v>-0.4203292041405058</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-0.028</v>
+        <v>-0.276</v>
       </c>
       <c r="AQ33">
-        <v>161.4285714285714</v>
+        <v>4.637681159420289</v>
       </c>
     </row>
     <row r="34">
@@ -4393,7 +4141,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Goldstone Investment Group Limited (SEHK:901)</t>
+          <t>Model Performance Acquisition Corp. (NasdaqCM:MPAC)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4401,32 +4149,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G34">
-        <v>2.231481481481481</v>
-      </c>
-      <c r="H34">
-        <v>2.231481481481481</v>
-      </c>
-      <c r="I34">
-        <v>2.518518518518519</v>
-      </c>
-      <c r="J34">
-        <v>2.518518518518519</v>
-      </c>
       <c r="K34">
-        <v>-5.01</v>
-      </c>
-      <c r="L34">
-        <v>4.638888888888888</v>
+        <v>-1.58</v>
       </c>
       <c r="M34">
-        <v>-0</v>
+        <v>36.3</v>
       </c>
       <c r="N34">
-        <v>-0</v>
+        <v>1.186274509803921</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>-22.97468354430379</v>
       </c>
       <c r="P34">
         <v>-0</v>
@@ -4438,70 +4171,61 @@
         <v>0</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>36.3</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
       </c>
       <c r="U34">
-        <v>0.147</v>
+        <v>0.442</v>
       </c>
       <c r="V34">
-        <v>0.00389920424403183</v>
+        <v>0.01444444444444444</v>
       </c>
       <c r="W34">
-        <v>0.3528169014084507</v>
+        <v>0.9349112426035504</v>
       </c>
       <c r="X34">
-        <v>0.06377523971476286</v>
+        <v>0.08124382044938905</v>
       </c>
       <c r="Y34">
-        <v>0.2890416616936879</v>
-      </c>
-      <c r="Z34">
-        <v>-2.240663900414938</v>
-      </c>
-      <c r="AA34">
-        <v>-5.643153526970955</v>
+        <v>0.8536674221541614</v>
       </c>
       <c r="AB34">
-        <v>0.05164979015378433</v>
-      </c>
-      <c r="AC34">
-        <v>-5.694803317124739</v>
+        <v>0.07914112890904292</v>
       </c>
       <c r="AD34">
-        <v>21.3</v>
+        <v>2.69</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>21.3</v>
+        <v>2.69</v>
       </c>
       <c r="AG34">
-        <v>21.153</v>
+        <v>2.248</v>
       </c>
       <c r="AH34">
-        <v>0.3610169491525424</v>
+        <v>0.08080504656052868</v>
       </c>
       <c r="AI34">
-        <v>1.251468860164512</v>
+        <v>-1.174672489082969</v>
       </c>
       <c r="AJ34">
-        <v>0.3594209301140129</v>
+        <v>0.06843643448611787</v>
       </c>
       <c r="AK34">
-        <v>1.253659693000652</v>
+        <v>-0.8228404099560759</v>
       </c>
       <c r="AL34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.36</v>
-      </c>
-      <c r="AO34">
-        <v>-2</v>
+        <v>-0.338</v>
       </c>
       <c r="AQ34">
-        <v>-2</v>
+        <v>5.857988165680473</v>
       </c>
     </row>
     <row r="35">
@@ -4512,7 +4236,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HH&amp;L Acquisition Co. (NYSE:HHLA)</t>
+          <t>Goldstone Capital Group Limited (SEHK:1160)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4520,8 +4244,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D35">
+        <v>2.595</v>
+      </c>
+      <c r="G35">
+        <v>-4.915032679738562</v>
+      </c>
+      <c r="H35">
+        <v>-4.915032679738562</v>
+      </c>
+      <c r="I35">
+        <v>-6.535947712418301</v>
+      </c>
+      <c r="J35">
+        <v>-6.535947712418301</v>
+      </c>
       <c r="K35">
-        <v>-0.038</v>
+        <v>-1.01</v>
+      </c>
+      <c r="L35">
+        <v>-6.601307189542484</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4545,46 +4287,64 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>0.475</v>
+        <v>3.61</v>
       </c>
       <c r="V35">
-        <v>0.0009433962264150943</v>
+        <v>0.1479508196721311</v>
+      </c>
+      <c r="W35">
+        <v>1.218335343787696</v>
       </c>
       <c r="X35">
-        <v>0.04817272237335087</v>
+        <v>0.0790328067232651</v>
+      </c>
+      <c r="Y35">
+        <v>1.139302537064431</v>
       </c>
       <c r="AB35">
-        <v>0.04817272237335087</v>
+        <v>0.07854437574621463</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="AG35">
-        <v>-0.475</v>
+        <v>-3.099</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>0.02051302637389105</v>
       </c>
       <c r="AI35">
-        <v>-0</v>
+        <v>0.1280380856928088</v>
       </c>
       <c r="AJ35">
-        <v>-0.0009442870632672333</v>
+        <v>-0.1454861274118586</v>
       </c>
       <c r="AK35">
-        <v>0.01650738488271069</v>
+        <v>-8.13385826771653</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>0.017</v>
+      </c>
+      <c r="AN35">
+        <v>-0.511</v>
+      </c>
+      <c r="AO35">
+        <v>-58.8235294117647</v>
+      </c>
+      <c r="AP35">
+        <v>3.099</v>
+      </c>
+      <c r="AQ35">
+        <v>-58.8235294117647</v>
       </c>
     </row>
     <row r="36">
@@ -4595,7 +4355,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Duddell Street Acquisition Corp. (NasdaqCM:DSAC)</t>
+          <t>Xenous Holdings, Inc. (OTCPK:XITO)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4604,7 +4364,7 @@
         </is>
       </c>
       <c r="K36">
-        <v>-27.3</v>
+        <v>-0.059</v>
       </c>
       <c r="M36">
         <v>-0</v>
@@ -4628,49 +4388,165 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0.099</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>0.0004562211981566821</v>
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.08613138686131386</v>
       </c>
       <c r="X36">
-        <v>0.04817272237335087</v>
+        <v>0.08037785579276718</v>
+      </c>
+      <c r="Y36">
+        <v>0.005753531068546675</v>
       </c>
       <c r="AB36">
-        <v>0.04817272237335087</v>
+        <v>0.07891637312236553</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="AG36">
-        <v>-0.099</v>
+        <v>0.734</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>0.0580971980370429</v>
       </c>
       <c r="AI36">
-        <v>-0</v>
+        <v>-81.55555555555549</v>
       </c>
       <c r="AJ36">
-        <v>-0.0004564294309385388</v>
+        <v>0.0580971980370429</v>
       </c>
       <c r="AK36">
-        <v>0.00543985933293038</v>
+        <v>-81.55555555555549</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-0.092</v>
-      </c>
-      <c r="AQ36">
-        <v>21.95652173913043</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Zijing International Financial Holdings Limited (SEHK:8340)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.083</v>
+      </c>
+      <c r="G37">
+        <v>0.3088</v>
+      </c>
+      <c r="H37">
+        <v>0.3088</v>
+      </c>
+      <c r="I37">
+        <v>-0.0824</v>
+      </c>
+      <c r="J37">
+        <v>-0.0824</v>
+      </c>
+      <c r="K37">
+        <v>-0.201</v>
+      </c>
+      <c r="L37">
+        <v>-0.0804</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0.09117481511966161</v>
+      </c>
+      <c r="AB37">
+        <v>0.0837526758000374</v>
+      </c>
+      <c r="AD37">
+        <v>1.1</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>1.1</v>
+      </c>
+      <c r="AG37">
+        <v>1.1</v>
+      </c>
+      <c r="AH37">
+        <v>0.2798982188295165</v>
+      </c>
+      <c r="AI37">
+        <v>0.222672064777328</v>
+      </c>
+      <c r="AJ37">
+        <v>0.2798982188295165</v>
+      </c>
+      <c r="AK37">
+        <v>0.222672064777328</v>
+      </c>
+      <c r="AL37">
+        <v>0.013</v>
+      </c>
+      <c r="AM37">
+        <v>0.013</v>
+      </c>
+      <c r="AN37">
+        <v>-4.741379310344827</v>
+      </c>
+      <c r="AO37">
+        <v>-15.84615384615385</v>
+      </c>
+      <c r="AP37">
+        <v>-4.741379310344827</v>
+      </c>
+      <c r="AQ37">
+        <v>-15.84615384615385</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0418</v>
+        <v>-0.154</v>
       </c>
       <c r="E2">
-        <v>-0.0441</v>
+        <v>-0.2445</v>
       </c>
       <c r="G2">
-        <v>0.1454849088318545</v>
+        <v>-0.6824874209041702</v>
       </c>
       <c r="H2">
-        <v>0.1394097567487312</v>
+        <v>-0.6937323702066022</v>
       </c>
       <c r="I2">
-        <v>-0.2306336402028712</v>
+        <v>-0.5922551313631601</v>
       </c>
       <c r="J2">
-        <v>-0.2274886360182866</v>
+        <v>-0.5877619465205146</v>
       </c>
       <c r="K2">
-        <v>-148.115</v>
+        <v>-179.868</v>
       </c>
       <c r="L2">
-        <v>-0.4035072425075394</v>
+        <v>-0.8570366699702676</v>
       </c>
       <c r="M2">
-        <v>159.08</v>
+        <v>528.649</v>
       </c>
       <c r="N2">
-        <v>0.02779884456902005</v>
+        <v>0.2284745572257133</v>
       </c>
       <c r="O2">
-        <v>-1.074030314282821</v>
+        <v>-2.939094224653635</v>
       </c>
       <c r="P2">
-        <v>18.72</v>
+        <v>8.387</v>
       </c>
       <c r="Q2">
-        <v>0.003271274643777064</v>
+        <v>0.003624741769022655</v>
       </c>
       <c r="R2">
-        <v>-0.1263882793775107</v>
+        <v>-0.04662863877954945</v>
       </c>
       <c r="S2">
-        <v>140.36</v>
+        <v>520.2619999999999</v>
       </c>
       <c r="T2">
-        <v>0.8823233593160674</v>
+        <v>0.9841350309940999</v>
       </c>
       <c r="U2">
-        <v>383.127</v>
+        <v>397.864</v>
       </c>
       <c r="V2">
-        <v>0.06695051498110979</v>
+        <v>0.1719511457243865</v>
       </c>
       <c r="W2">
-        <v>-0.2441821247892074</v>
+        <v>-0.07546513816730668</v>
       </c>
       <c r="X2">
-        <v>0.07920747068752179</v>
+        <v>0.06723613137144929</v>
       </c>
       <c r="Y2">
-        <v>-0.3233895954767292</v>
+        <v>-0.142701269538756</v>
       </c>
       <c r="Z2">
-        <v>0.135797864001565</v>
+        <v>0.06491582245299836</v>
       </c>
       <c r="AA2">
-        <v>-0.3429791271347248</v>
+        <v>-0.1238887270921606</v>
       </c>
       <c r="AB2">
-        <v>0.07854437574621463</v>
+        <v>0.06695681654484614</v>
       </c>
       <c r="AC2">
-        <v>-0.4221811415847984</v>
+        <v>-0.1913832391755795</v>
       </c>
       <c r="AD2">
-        <v>830.385</v>
+        <v>235.902</v>
       </c>
       <c r="AE2">
-        <v>0.02729837813867119</v>
+        <v>0.05384464724563817</v>
       </c>
       <c r="AF2">
-        <v>830.4122983781386</v>
+        <v>235.9558446472456</v>
       </c>
       <c r="AG2">
-        <v>447.2852983781386</v>
+        <v>-161.9081553527543</v>
       </c>
       <c r="AH2">
-        <v>0.1267233852112225</v>
+        <v>0.09253983841073271</v>
       </c>
       <c r="AI2">
-        <v>0.2429790436230802</v>
+        <v>0.06820806868668455</v>
       </c>
       <c r="AJ2">
-        <v>0.07249561806810259</v>
+        <v>-0.07523921379748495</v>
       </c>
       <c r="AK2">
-        <v>0.1473998878225272</v>
+        <v>-0.05288541317092296</v>
       </c>
       <c r="AL2">
-        <v>25.637</v>
+        <v>17.287</v>
       </c>
       <c r="AM2">
-        <v>11.014</v>
+        <v>2.465999999999999</v>
       </c>
       <c r="AN2">
-        <v>63.7189226519337</v>
+        <v>-3.403479916897507</v>
       </c>
       <c r="AO2">
-        <v>-3.303116589304521</v>
+        <v>-7.192919534910627</v>
       </c>
       <c r="AP2">
-        <v>34.32207630280376</v>
+        <v>2.335932527596294</v>
       </c>
       <c r="AQ2">
-        <v>-7.688578173234065</v>
+        <v>-50.42335766423359</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sheng Yuan Holdings Limited (SEHK:851)</t>
+          <t>Cocoon Holdings Limited (SEHK:428)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,26 +721,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0833</v>
-      </c>
       <c r="G3">
-        <v>0.2974607013301088</v>
+        <v>-0.02309442548350399</v>
       </c>
       <c r="H3">
-        <v>0.2974607013301088</v>
+        <v>-0.02309442548350399</v>
       </c>
       <c r="I3">
-        <v>0.3821039903264813</v>
+        <v>0.9089874857792948</v>
       </c>
       <c r="J3">
-        <v>0.1997361767615698</v>
+        <v>0.9089874857792948</v>
       </c>
       <c r="K3">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="L3">
-        <v>0.1257557436517533</v>
+        <v>0.2354948805460751</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +761,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.84</v>
+        <v>0.025</v>
       </c>
       <c r="V3">
-        <v>0.6173228346456693</v>
+        <v>0.001470588235294118</v>
       </c>
       <c r="W3">
-        <v>-0.2321428571428571</v>
+        <v>0.1468085106382979</v>
       </c>
       <c r="X3">
-        <v>0.1274769118152398</v>
+        <v>0.06927678975106152</v>
       </c>
       <c r="Y3">
-        <v>-0.359619768958097</v>
+        <v>0.07753172088723634</v>
       </c>
       <c r="Z3">
-        <v>2.022004889975551</v>
+        <v>0.5362044775208931</v>
       </c>
       <c r="AA3">
-        <v>0.4038675261169151</v>
+        <v>0.487403159885317</v>
       </c>
       <c r="AB3">
-        <v>0.08990456335307645</v>
+        <v>0.06743585642319293</v>
       </c>
       <c r="AC3">
-        <v>0.3139629627638386</v>
+        <v>0.4199673034621241</v>
       </c>
       <c r="AD3">
-        <v>18.9</v>
+        <v>1.81</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>11.06</v>
+        <v>1.785</v>
       </c>
       <c r="AH3">
-        <v>0.5981012658227848</v>
+        <v>0.09622541201488571</v>
       </c>
       <c r="AI3">
-        <v>1.219354838709678</v>
+        <v>0.08697741470446901</v>
       </c>
       <c r="AJ3">
-        <v>0.4654882154882155</v>
+        <v>0.09502262443438915</v>
       </c>
       <c r="AK3">
-        <v>1.443864229765013</v>
+        <v>0.0858792398364205</v>
       </c>
       <c r="AL3">
-        <v>1.19</v>
+        <v>0.249</v>
       </c>
       <c r="AM3">
-        <v>1.19</v>
+        <v>0.249</v>
       </c>
       <c r="AN3">
-        <v>5.815384615384615</v>
+        <v>0.2265331664580726</v>
       </c>
       <c r="AO3">
-        <v>2.65546218487395</v>
+        <v>32.08835341365462</v>
       </c>
       <c r="AP3">
-        <v>3.403076923076923</v>
+        <v>0.223404255319149</v>
       </c>
       <c r="AQ3">
-        <v>2.65546218487395</v>
+        <v>32.08835341365462</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Value Partners Group Limited (SEHK:806)</t>
+          <t>Somerley Capital Holdings Limited (SEHK:8439)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,118 +847,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0764</v>
+        <v>-0.0304</v>
+      </c>
+      <c r="E4">
+        <v>-0.312</v>
       </c>
       <c r="G4">
-        <v>0.3933437744714173</v>
+        <v>-0.06531728665207877</v>
       </c>
       <c r="H4">
-        <v>0.3758809710258418</v>
+        <v>-0.06531728665207877</v>
       </c>
       <c r="I4">
-        <v>0.1213782302270947</v>
+        <v>0.04365426695842451</v>
       </c>
       <c r="J4">
-        <v>0.1213782302270947</v>
+        <v>0.04134562784043091</v>
       </c>
       <c r="K4">
-        <v>-23</v>
+        <v>0.211</v>
       </c>
       <c r="L4">
-        <v>-0.1801096319498825</v>
+        <v>0.02308533916849015</v>
       </c>
       <c r="M4">
-        <v>25.527</v>
+        <v>0.479</v>
       </c>
       <c r="N4">
-        <v>0.03783459315251222</v>
+        <v>0.03446043165467626</v>
       </c>
       <c r="O4">
-        <v>-1.109869565217391</v>
+        <v>2.270142180094787</v>
       </c>
       <c r="P4">
-        <v>18.267</v>
+        <v>0.457</v>
       </c>
       <c r="Q4">
-        <v>0.02707425522454424</v>
+        <v>0.03287769784172662</v>
       </c>
       <c r="R4">
-        <v>-0.7942173913043478</v>
+        <v>2.165876777251185</v>
       </c>
       <c r="S4">
-        <v>7.260000000000002</v>
+        <v>0.02200000000000002</v>
       </c>
       <c r="T4">
-        <v>0.2844047479139735</v>
+        <v>0.04592901878914409</v>
       </c>
       <c r="U4">
-        <v>204.4</v>
+        <v>8.31</v>
       </c>
       <c r="V4">
-        <v>0.3029494590188231</v>
+        <v>0.597841726618705</v>
       </c>
       <c r="W4">
-        <v>-0.03560371517027864</v>
+        <v>0.02009523809523809</v>
       </c>
       <c r="X4">
-        <v>0.07906070076279677</v>
+        <v>0.06829163208291605</v>
       </c>
       <c r="Y4">
-        <v>-0.1146644159330754</v>
+        <v>-0.04819639398767796</v>
       </c>
       <c r="Z4">
-        <v>0.3083051665861903</v>
+        <v>2.517906336088155</v>
       </c>
       <c r="AA4">
-        <v>0.0374215354901014</v>
+        <v>0.1041044183089638</v>
       </c>
       <c r="AB4">
-        <v>0.07848473401109766</v>
+        <v>0.0670603773402859</v>
       </c>
       <c r="AC4">
-        <v>-0.04106319852099626</v>
+        <v>0.0370440409686779</v>
       </c>
       <c r="AD4">
-        <v>14.7</v>
+        <v>0.894</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.7</v>
+        <v>0.894</v>
       </c>
       <c r="AG4">
-        <v>-189.7</v>
+        <v>-7.416</v>
       </c>
       <c r="AH4">
-        <v>0.02132288946910357</v>
+        <v>0.06042990401514127</v>
       </c>
       <c r="AI4">
-        <v>0.0242094861660079</v>
+        <v>0.07986421297123458</v>
       </c>
       <c r="AJ4">
-        <v>-0.3911340206185567</v>
+        <v>-1.143738433066009</v>
       </c>
       <c r="AK4">
-        <v>-0.470953326713009</v>
+        <v>-2.571428571428571</v>
       </c>
       <c r="AL4">
-        <v>0.603</v>
+        <v>0.045</v>
       </c>
       <c r="AM4">
-        <v>0.603</v>
+        <v>0.045</v>
       </c>
       <c r="AN4">
-        <v>0.8647058823529411</v>
+        <v>1.820773930753564</v>
       </c>
       <c r="AO4">
-        <v>25.70480928689884</v>
+        <v>8.866666666666667</v>
       </c>
       <c r="AP4">
-        <v>-11.15882352941177</v>
+        <v>-15.10386965376782</v>
       </c>
       <c r="AQ4">
-        <v>25.70480928689884</v>
+        <v>8.866666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CST Group Limited (SEHK:985)</t>
+          <t>Goldstream Investment Limited (SEHK:1328)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,25 +981,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.452</v>
+        <v>-0.274</v>
       </c>
       <c r="G5">
-        <v>0.1934865900383142</v>
+        <v>-1.315868263473054</v>
       </c>
       <c r="H5">
-        <v>0.1934865900383142</v>
+        <v>-1.315868263473054</v>
       </c>
       <c r="I5">
-        <v>0.1698595146871009</v>
+        <v>0.3008982035928143</v>
       </c>
       <c r="J5">
-        <v>0.1698595146871009</v>
+        <v>0.3008982035928143</v>
       </c>
       <c r="K5">
-        <v>-72.40000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="L5">
-        <v>-0.4623243933588762</v>
+        <v>0.3023952095808383</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,7 +1008,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1017,79 +1017,79 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>71.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="V5">
-        <v>0.5835370823145883</v>
+        <v>0.2621359223300971</v>
       </c>
       <c r="W5">
-        <v>-0.2441821247892074</v>
+        <v>0.02121848739495798</v>
       </c>
       <c r="X5">
-        <v>0.2086065461055711</v>
+        <v>0.06680259498207133</v>
       </c>
       <c r="Y5">
-        <v>-0.4527886708947786</v>
+        <v>-0.04558410758711335</v>
       </c>
       <c r="Z5">
-        <v>0.216507673164662</v>
+        <v>0.1216093209539414</v>
       </c>
       <c r="AA5">
-        <v>0.03677588828978294</v>
+        <v>0.03659202621518295</v>
       </c>
       <c r="AB5">
-        <v>0.08370626453053831</v>
+        <v>0.06679257430616937</v>
       </c>
       <c r="AC5">
-        <v>-0.04693037624075537</v>
+        <v>-0.03020054809098642</v>
       </c>
       <c r="AD5">
-        <v>484.1</v>
+        <v>0.031</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>484.1</v>
+        <v>0.031</v>
       </c>
       <c r="AG5">
-        <v>412.5</v>
+        <v>-13.469</v>
       </c>
       <c r="AH5">
-        <v>0.7977916941331575</v>
+        <v>0.0006015796316780191</v>
       </c>
       <c r="AI5">
-        <v>0.6928581651638758</v>
+        <v>0.000316872974823931</v>
       </c>
       <c r="AJ5">
-        <v>0.7707399103139013</v>
+        <v>-0.3541584496857826</v>
       </c>
       <c r="AK5">
-        <v>0.6577898261840217</v>
+        <v>-0.1597158814670762</v>
       </c>
       <c r="AL5">
-        <v>10.4</v>
+        <v>0.04</v>
       </c>
       <c r="AM5">
-        <v>10.092</v>
+        <v>0.04</v>
       </c>
       <c r="AN5">
-        <v>8.261092150170649</v>
+        <v>0.01297071129707113</v>
       </c>
       <c r="AO5">
-        <v>2.557692307692308</v>
+        <v>50.24999999999999</v>
       </c>
       <c r="AP5">
-        <v>7.039249146757679</v>
+        <v>-5.635564853556485</v>
       </c>
       <c r="AQ5">
-        <v>2.635751089972255</v>
+        <v>50.24999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wealthking Investments Limited (SEHK:1140)</t>
+          <t>Prestige Wealth Inc. (NasdaqCM:PWM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1108,29 +1108,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0597</v>
-      </c>
-      <c r="E6">
-        <v>-0.0441</v>
-      </c>
       <c r="G6">
-        <v>0.7245508982035929</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.7245508982035929</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.6347305389221557</v>
+        <v>0.2080076548302905</v>
       </c>
       <c r="J6">
-        <v>0.6347305389221557</v>
+        <v>0.2080076548302905</v>
       </c>
       <c r="K6">
-        <v>30.3</v>
+        <v>0.288</v>
       </c>
       <c r="L6">
-        <v>1.81437125748503</v>
+        <v>0.3344947735191637</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1154,73 +1148,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.51</v>
+        <v>0.473</v>
       </c>
       <c r="V6">
-        <v>0.007017193122750899</v>
+        <v>0.02502645502645503</v>
       </c>
       <c r="W6">
-        <v>0.04606263301915476</v>
+        <v>0.05413533834586465</v>
       </c>
       <c r="X6">
-        <v>0.09045374578462688</v>
+        <v>0.06681885578287858</v>
       </c>
       <c r="Y6">
-        <v>-0.04439111276547212</v>
+        <v>-0.01268351743701392</v>
       </c>
       <c r="Z6">
-        <v>0.02382990867579909</v>
+        <v>0.1643591781519453</v>
       </c>
       <c r="AA6">
-        <v>0.01512557077625571</v>
+        <v>0.03418796719722005</v>
       </c>
       <c r="AB6">
-        <v>0.08099781653500006</v>
+        <v>0.06679724612687926</v>
       </c>
       <c r="AC6">
-        <v>-0.06587224575874435</v>
+        <v>-0.03260927892965921</v>
       </c>
       <c r="AD6">
-        <v>183.5</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.02452704595559947</v>
       </c>
       <c r="AF6">
-        <v>183.5</v>
+        <v>0.02452704595559947</v>
       </c>
       <c r="AG6">
-        <v>179.99</v>
+        <v>-0.4484729540444005</v>
       </c>
       <c r="AH6">
-        <v>0.2683925698405734</v>
+        <v>0.001296045385759915</v>
       </c>
       <c r="AI6">
-        <v>0.1297461641801598</v>
+        <v>0.0043452791980461</v>
       </c>
       <c r="AJ6">
-        <v>0.2646172393007836</v>
+        <v>-0.02430546550035823</v>
       </c>
       <c r="AK6">
-        <v>0.1275810007159109</v>
+        <v>-0.08671963813766177</v>
       </c>
       <c r="AL6">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>16.23893805309734</v>
-      </c>
-      <c r="AO6">
-        <v>1.556534508076358</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>15.9283185840708</v>
-      </c>
-      <c r="AQ6">
-        <v>1.556534508076358</v>
+        <v>-17.24895977093848</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Central Wealth Group Holdings Limited (SEHK:139)</t>
+          <t>China Innovation Investment Limited (SEHK:1217)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1239,23 +1227,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.154</v>
+      </c>
+      <c r="E7">
+        <v>-0.177</v>
+      </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.3526315789473685</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.3526315789473685</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.6507177033492824</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.6507177033492824</v>
       </c>
       <c r="K7">
-        <v>-37</v>
+        <v>1.36</v>
       </c>
       <c r="L7">
-        <v>-1.048158640226629</v>
+        <v>0.6507177033492824</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1264,7 +1258,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1273,67 +1267,73 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>12.7</v>
+        <v>0.472</v>
       </c>
       <c r="V7">
-        <v>0.05390492359932088</v>
+        <v>0.02878048780487805</v>
       </c>
       <c r="W7">
-        <v>-0.24983119513842</v>
+        <v>0.01741357234314981</v>
       </c>
       <c r="X7">
-        <v>0.08529229567557928</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y7">
-        <v>-0.3351234908139993</v>
+        <v>-0.049374955007262</v>
       </c>
       <c r="Z7">
-        <v>0.1641097164109716</v>
+        <v>0.02716437697396639</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.01767634099741354</v>
       </c>
       <c r="AB7">
-        <v>0.08479677217555831</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC7">
-        <v>-0.08479677217555831</v>
+        <v>-0.04911218635299827</v>
       </c>
       <c r="AD7">
-        <v>49.6</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>49.6</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>36.90000000000001</v>
+        <v>-0.472</v>
       </c>
       <c r="AH7">
-        <v>0.1739130434782609</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.2618796198521647</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.1354128440366973</v>
+        <v>-0.02963335007533903</v>
       </c>
       <c r="AK7">
-        <v>0.2088285229202037</v>
+        <v>-0.006525826789072005</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.004</v>
+      </c>
+      <c r="AO7">
+        <v>340</v>
+      </c>
+      <c r="AQ7">
+        <v>340</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UBA Investments Limited (SEHK:768)</t>
+          <t>Ding Yi Feng Holdings Group International Limited (SEHK:612)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,25 +1353,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.289</v>
+        <v>0.718</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-2.114754098360656</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-2.114754098360656</v>
       </c>
       <c r="I8">
-        <v>-0.2086811352253756</v>
+        <v>0.1562841530054645</v>
       </c>
       <c r="J8">
-        <v>-0.2086811352253756</v>
+        <v>0.133722004156084</v>
       </c>
       <c r="K8">
-        <v>-1.67</v>
+        <v>4.86</v>
       </c>
       <c r="L8">
-        <v>-2.787979966611018</v>
+        <v>0.2655737704918033</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1380,7 +1380,7 @@
         <v>-0</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8">
         <v>-0</v>
@@ -1389,67 +1389,79 @@
         <v>-0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.613</v>
+        <v>32.1</v>
       </c>
       <c r="V8">
-        <v>0.1211462450592885</v>
+        <v>0.09502664298401421</v>
       </c>
       <c r="W8">
-        <v>-0.1265151515151515</v>
+        <v>0.03509025270758123</v>
       </c>
       <c r="X8">
-        <v>0.0783413436811104</v>
+        <v>0.06757722714866099</v>
       </c>
       <c r="Y8">
-        <v>-0.2048564951962619</v>
+        <v>-0.03248697444107976</v>
       </c>
       <c r="Z8">
-        <v>0.04702834262385177</v>
+        <v>0.127972027972028</v>
       </c>
       <c r="AA8">
-        <v>-0.009813927926513307</v>
+        <v>0.01711267605633802</v>
       </c>
       <c r="AB8">
-        <v>0.0783413436811104</v>
+        <v>0.067008144347736</v>
       </c>
       <c r="AC8">
-        <v>-0.08815527160762371</v>
+        <v>-0.04989546829139797</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="AG8">
-        <v>-0.613</v>
+        <v>-20.7</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.03264604810996564</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.06006322444678609</v>
       </c>
       <c r="AJ8">
-        <v>-0.1378457387002474</v>
+        <v>-0.065279091769158</v>
       </c>
       <c r="AK8">
-        <v>-0.05682766292759803</v>
+        <v>-0.1312618896639189</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="AN8">
+        <v>2.579185520361991</v>
+      </c>
+      <c r="AO8">
+        <v>2.072463768115942</v>
+      </c>
+      <c r="AP8">
+        <v>-4.683257918552037</v>
+      </c>
+      <c r="AQ8">
+        <v>2.072463768115942</v>
       </c>
     </row>
     <row r="9">
@@ -1460,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Walnut Capital Limited (SEHK:905)</t>
+          <t>Wealthink AI-Innovation Capital Limited (SEHK:1140)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1469,25 +1481,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0401</v>
+        <v>0.0322</v>
       </c>
       <c r="G9">
-        <v>-2.069392812887236</v>
+        <v>0.5169230769230769</v>
       </c>
       <c r="H9">
-        <v>-2.069392812887236</v>
+        <v>0.5169230769230769</v>
       </c>
       <c r="I9">
-        <v>-2.168525402726146</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="J9">
-        <v>-2.168525402726146</v>
+        <v>0.7538461538461538</v>
       </c>
       <c r="K9">
-        <v>-18.1</v>
+        <v>-5.58</v>
       </c>
       <c r="L9">
-        <v>-22.42874845105328</v>
+        <v>-0.1716923076923077</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1511,73 +1523,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.478</v>
+        <v>4.39</v>
       </c>
       <c r="V9">
-        <v>0.03229729729729729</v>
+        <v>0.008577569363032434</v>
       </c>
       <c r="W9">
-        <v>-0.4480198019801981</v>
+        <v>-0.004533636659083523</v>
       </c>
       <c r="X9">
-        <v>0.08532399765258109</v>
+        <v>0.07373389845894646</v>
       </c>
       <c r="Y9">
-        <v>-0.5333437996327792</v>
+        <v>-0.07826753511802997</v>
       </c>
       <c r="Z9">
-        <v>0.01784766454352442</v>
+        <v>0.02303673828138844</v>
       </c>
       <c r="AA9">
-        <v>-0.03870311394196745</v>
+        <v>0.01736615655058513</v>
       </c>
       <c r="AB9">
-        <v>0.08006916545070474</v>
+        <v>0.08179260594218853</v>
       </c>
       <c r="AC9">
-        <v>-0.1187722793926722</v>
+        <v>-0.06442644939160339</v>
       </c>
       <c r="AD9">
-        <v>3.13</v>
+        <v>152.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3.13</v>
+        <v>152.1</v>
       </c>
       <c r="AG9">
-        <v>2.652</v>
+        <v>147.71</v>
       </c>
       <c r="AH9">
-        <v>0.1745677635248187</v>
+        <v>0.2291007681879801</v>
       </c>
       <c r="AI9">
-        <v>0.1255515443241075</v>
+        <v>0.1076814159292035</v>
       </c>
       <c r="AJ9">
-        <v>0.1519596607838643</v>
+        <v>0.2239693105487408</v>
       </c>
       <c r="AK9">
-        <v>0.108457385898904</v>
+        <v>0.1048994751830468</v>
       </c>
       <c r="AL9">
-        <v>0.104</v>
+        <v>11.2</v>
       </c>
       <c r="AM9">
-        <v>0.104</v>
+        <v>11.2</v>
       </c>
       <c r="AN9">
-        <v>-1.874251497005988</v>
+        <v>6.084</v>
       </c>
       <c r="AO9">
-        <v>-16.82692307692308</v>
+        <v>2.1875</v>
       </c>
       <c r="AP9">
-        <v>-1.588023952095809</v>
+        <v>5.9084</v>
       </c>
       <c r="AQ9">
-        <v>-16.82692307692308</v>
+        <v>2.1875</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harbour Digital Asset Capital Limited (SEHK:913)</t>
+          <t>UBA Investments Limited (SEHK:768)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1596,6 +1608,9 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.0386</v>
+      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1603,16 +1618,16 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>-7.748917748917749</v>
+        <v>-0.001612903225806452</v>
       </c>
       <c r="J10">
-        <v>-7.748917748917749</v>
+        <v>-0.001612903225806452</v>
       </c>
       <c r="K10">
-        <v>-9.369999999999999</v>
+        <v>-0.897</v>
       </c>
       <c r="L10">
-        <v>-40.56277056277056</v>
+        <v>-1.446774193548387</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1636,31 +1651,31 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1.28</v>
+        <v>0.908</v>
       </c>
       <c r="V10">
-        <v>0.06124401913875599</v>
+        <v>0.2785276073619632</v>
       </c>
       <c r="W10">
-        <v>-0.2928125</v>
+        <v>-0.07868421052631579</v>
       </c>
       <c r="X10">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y10">
-        <v>-0.3711538436811104</v>
+        <v>-0.1454727378767276</v>
       </c>
       <c r="Z10">
-        <v>0.007633840052875082</v>
+        <v>0.05747659219430796</v>
       </c>
       <c r="AA10">
-        <v>-0.05915399867812293</v>
+        <v>-9.270418095856123e-05</v>
       </c>
       <c r="AB10">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC10">
-        <v>-0.1374953423592333</v>
+        <v>-0.06688123153137038</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1672,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>-1.28</v>
+        <v>-0.908</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -1681,16 +1696,19 @@
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-0.06523955147808359</v>
+        <v>-0.3860544217687075</v>
       </c>
       <c r="AK10">
-        <v>-0.05683836589698046</v>
+        <v>-0.09466221851542952</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AQ10">
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -1701,7 +1719,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>China Innovation Investment Limited (SEHK:1217)</t>
+          <t>Central Wealth Group Holdings Limited (SEHK:139)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1709,8 +1727,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="K11">
-        <v>-5.35</v>
+        <v>-10.1</v>
+      </c>
+      <c r="L11">
+        <v>-0.5343915343915344</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1734,67 +1767,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1.28</v>
+        <v>5.66</v>
       </c>
       <c r="V11">
-        <v>0.07804878048780489</v>
+        <v>0.1466321243523316</v>
       </c>
       <c r="W11">
-        <v>-0.06257309941520467</v>
+        <v>-0.07224606580829757</v>
       </c>
       <c r="X11">
-        <v>0.07858091841372464</v>
+        <v>0.08464934082085272</v>
       </c>
       <c r="Y11">
-        <v>-0.1411540178289293</v>
+        <v>-0.1568954066291503</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>0.1069609507640068</v>
       </c>
       <c r="AA11">
-        <v>-0.06354722010662604</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07834347035023843</v>
+        <v>0.07236304851863103</v>
       </c>
       <c r="AC11">
-        <v>-0.1418906904568645</v>
+        <v>-0.07236304851863103</v>
       </c>
       <c r="AD11">
-        <v>0.119</v>
+        <v>29.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.119</v>
+        <v>29.5</v>
       </c>
       <c r="AG11">
-        <v>-1.161</v>
+        <v>23.84</v>
       </c>
       <c r="AH11">
-        <v>0.00720382589745142</v>
+        <v>0.433186490455213</v>
       </c>
       <c r="AI11">
-        <v>0.00152136948823176</v>
+        <v>0.1766467065868264</v>
       </c>
       <c r="AJ11">
-        <v>-0.0761861014502264</v>
+        <v>0.381806534272902</v>
       </c>
       <c r="AK11">
-        <v>-0.01508987639558612</v>
+        <v>0.1477624891533408</v>
       </c>
       <c r="AL11">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.014</v>
-      </c>
-      <c r="AO11">
-        <v>-381.4285714285714</v>
-      </c>
-      <c r="AQ11">
-        <v>-381.4285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1805,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>China Investment Fund Company Limited (SEHK:612)</t>
+          <t>Value Partners Group Limited (SEHK:806)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1813,113 +1840,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.329</v>
+      </c>
       <c r="G12">
-        <v>5.253623188405798</v>
+        <v>-0.06763157894736843</v>
       </c>
       <c r="H12">
-        <v>5.253623188405798</v>
+        <v>-0.09868421052631579</v>
       </c>
       <c r="I12">
-        <v>-9.420289855072465</v>
+        <v>-0.0446692568455001</v>
       </c>
       <c r="J12">
-        <v>-9.420289855072465</v>
+        <v>-0.0446692568455001</v>
       </c>
       <c r="K12">
-        <v>-7.47</v>
+        <v>-14.1</v>
       </c>
       <c r="L12">
-        <v>-5.41304347826087</v>
+        <v>-0.1855263157894737</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>10.57</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.02112310151878498</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0.749645390070922</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>7.93</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.01584732214228617</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0.5624113475177305</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.640000000000001</v>
+      </c>
+      <c r="T12">
+        <v>0.2497634815515611</v>
       </c>
       <c r="U12">
-        <v>18.3</v>
+        <v>194.1</v>
       </c>
       <c r="V12">
-        <v>0.02954949136121428</v>
+        <v>0.3878896882494005</v>
       </c>
       <c r="W12">
-        <v>-0.0540520984081042</v>
+        <v>-0.02379746835443038</v>
       </c>
       <c r="X12">
-        <v>0.0795568904290532</v>
+        <v>0.06735033831907002</v>
       </c>
       <c r="Y12">
-        <v>-0.1336089888371574</v>
+        <v>-0.09114780667350039</v>
       </c>
       <c r="Z12">
-        <v>0.009663865546218488</v>
+        <v>0.1886655133557653</v>
       </c>
       <c r="AA12">
-        <v>-0.09103641456582634</v>
+        <v>-0.008427548273976808</v>
       </c>
       <c r="AB12">
-        <v>0.07858012810039418</v>
+        <v>0.06689413234024065</v>
       </c>
       <c r="AC12">
-        <v>-0.1696165426662205</v>
+        <v>-0.07532168061421746</v>
       </c>
       <c r="AD12">
-        <v>22.8</v>
+        <v>12</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.02931760129003871</v>
       </c>
       <c r="AF12">
-        <v>22.8</v>
+        <v>12.02931760129004</v>
       </c>
       <c r="AG12">
-        <v>4.5</v>
+        <v>-182.0706823987099</v>
       </c>
       <c r="AH12">
-        <v>0.03550848777448996</v>
+        <v>0.02347507683127878</v>
       </c>
       <c r="AI12">
-        <v>0.1413515189088655</v>
+        <v>0.02081811572183056</v>
       </c>
       <c r="AJ12">
-        <v>0.007213850593138827</v>
+        <v>-0.5719570028003356</v>
       </c>
       <c r="AK12">
-        <v>0.03146853146853147</v>
+        <v>-0.4744768618067609</v>
       </c>
       <c r="AL12">
-        <v>2.46</v>
+        <v>0.796</v>
       </c>
       <c r="AM12">
-        <v>2.46</v>
+        <v>0.796</v>
       </c>
       <c r="AN12">
-        <v>-2.017699115044248</v>
+        <v>-5.583992554676594</v>
       </c>
       <c r="AO12">
-        <v>-5.284552845528455</v>
+        <v>-4.296482412060302</v>
       </c>
       <c r="AP12">
-        <v>-0.3982300884955752</v>
+        <v>84.72344457827359</v>
       </c>
       <c r="AQ12">
-        <v>-5.284552845528455</v>
+        <v>-4.296482412060302</v>
       </c>
     </row>
     <row r="13">
@@ -1930,7 +1963,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Goldstone Investment Group Limited (SEHK:901)</t>
+          <t>Capital Realm Financial Holdings Group Limited (SEHK:204)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1938,8 +1971,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.481</v>
+      </c>
+      <c r="G13">
+        <v>-1.962264150943396</v>
+      </c>
+      <c r="H13">
+        <v>-1.962264150943396</v>
+      </c>
+      <c r="I13">
+        <v>-1.141509433962264</v>
+      </c>
+      <c r="J13">
+        <v>-1.141509433962264</v>
+      </c>
       <c r="K13">
-        <v>-4.36</v>
+        <v>2.06</v>
+      </c>
+      <c r="L13">
+        <v>1.943396226415094</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1948,7 +1999,7 @@
         <v>-0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -1957,73 +2008,79 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.419</v>
+        <v>1.02</v>
       </c>
       <c r="V13">
-        <v>0.02950704225352113</v>
+        <v>0.01455064194008559</v>
       </c>
       <c r="W13">
-        <v>1.018691588785047</v>
+        <v>0.07923076923076923</v>
       </c>
       <c r="X13">
-        <v>0.1306570475127204</v>
+        <v>0.06698655915755206</v>
       </c>
       <c r="Y13">
-        <v>0.8880345412723263</v>
+        <v>0.01224421007321717</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>0.03779639864503476</v>
       </c>
       <c r="AA13">
-        <v>-0.1416464173531678</v>
+        <v>-0.04314494562310572</v>
       </c>
       <c r="AB13">
-        <v>0.08440942437509404</v>
+        <v>0.06710941553247367</v>
       </c>
       <c r="AC13">
-        <v>-0.2260558417282618</v>
+        <v>-0.1102543611555794</v>
       </c>
       <c r="AD13">
-        <v>22.5</v>
+        <v>0.594</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>22.5</v>
+        <v>0.594</v>
       </c>
       <c r="AG13">
-        <v>22.081</v>
+        <v>-0.426</v>
       </c>
       <c r="AH13">
-        <v>0.6130790190735694</v>
+        <v>0.008402410388434664</v>
       </c>
       <c r="AI13">
-        <v>1.573426573426573</v>
+        <v>0.01356350184956843</v>
       </c>
       <c r="AJ13">
-        <v>0.6086105675146771</v>
+        <v>-0.00611418893704969</v>
       </c>
       <c r="AK13">
-        <v>1.590735537785462</v>
+        <v>-0.009959321082900829</v>
       </c>
       <c r="AL13">
-        <v>1.95</v>
+        <v>0.407</v>
       </c>
       <c r="AM13">
-        <v>1.95</v>
+        <v>0.407</v>
+      </c>
+      <c r="AN13">
+        <v>-0.4991596638655462</v>
       </c>
       <c r="AO13">
-        <v>-1.225641025641026</v>
+        <v>-2.972972972972973</v>
+      </c>
+      <c r="AP13">
+        <v>0.357983193277311</v>
       </c>
       <c r="AQ13">
-        <v>-1.225641025641026</v>
+        <v>-2.972972972972973</v>
       </c>
     </row>
     <row r="14">
@@ -2034,7 +2091,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital VC Limited (SEHK:2324)</t>
+          <t>Walnut Capital Limited (SEHK:905)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2042,8 +2099,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.476</v>
+      </c>
+      <c r="G14">
+        <v>-108.5714285714286</v>
+      </c>
+      <c r="H14">
+        <v>-108.5714285714286</v>
+      </c>
+      <c r="I14">
+        <v>-95.23809523809523</v>
+      </c>
+      <c r="J14">
+        <v>-95.23809523809523</v>
+      </c>
       <c r="K14">
-        <v>-11.2</v>
+        <v>-10.8</v>
+      </c>
+      <c r="L14">
+        <v>-514.2857142857143</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2067,67 +2142,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2.13</v>
+        <v>0.197</v>
       </c>
       <c r="V14">
-        <v>0.301699716713881</v>
+        <v>0.01841121495327103</v>
       </c>
       <c r="W14">
-        <v>-0.1651917404129793</v>
+        <v>-0.4954128440366973</v>
       </c>
       <c r="X14">
-        <v>0.08774137401640666</v>
+        <v>0.06958424118518941</v>
       </c>
       <c r="Y14">
-        <v>-0.252933114429386</v>
+        <v>-0.5649970852218866</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>0.0008588254539505972</v>
       </c>
       <c r="AA14">
-        <v>-0.1629696695337257</v>
+        <v>-0.08179290037624735</v>
       </c>
       <c r="AB14">
-        <v>0.08053477309947665</v>
+        <v>0.06750729493817485</v>
       </c>
       <c r="AC14">
-        <v>-0.2435044426332023</v>
+        <v>-0.1493001953144222</v>
       </c>
       <c r="AD14">
-        <v>2.01</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.01</v>
+        <v>1.28</v>
       </c>
       <c r="AG14">
-        <v>-0.1200000000000001</v>
+        <v>1.083</v>
       </c>
       <c r="AH14">
-        <v>0.2216097023153252</v>
+        <v>0.1068447412353923</v>
       </c>
       <c r="AI14">
-        <v>0.03257170636849781</v>
+        <v>0.1042345276872964</v>
       </c>
       <c r="AJ14">
-        <v>-0.01729106628242076</v>
+        <v>0.09191207672069932</v>
       </c>
       <c r="AK14">
-        <v>-0.002014098690835853</v>
+        <v>0.08963005876024166</v>
       </c>
       <c r="AL14">
-        <v>0.391</v>
+        <v>0.06</v>
       </c>
       <c r="AM14">
-        <v>0.391</v>
+        <v>0.06</v>
+      </c>
+      <c r="AN14">
+        <v>-0.6432160804020101</v>
       </c>
       <c r="AO14">
-        <v>-27.62148337595908</v>
+        <v>-33.33333333333334</v>
+      </c>
+      <c r="AP14">
+        <v>-0.5442211055276381</v>
       </c>
       <c r="AQ14">
-        <v>-27.62148337595908</v>
+        <v>-33.33333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2138,7 +2219,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCI International Holdings Limited (SEHK:329)</t>
+          <t>Jade Road Investments Limited (AIM:JADE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2146,26 +2227,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.0993</v>
-      </c>
-      <c r="G15">
-        <v>-4.188811188811189</v>
-      </c>
-      <c r="H15">
-        <v>-4.188811188811189</v>
-      </c>
-      <c r="I15">
-        <v>-9.23076923076923</v>
-      </c>
-      <c r="J15">
-        <v>-9.23076923076923</v>
-      </c>
       <c r="K15">
-        <v>-22.3</v>
-      </c>
-      <c r="L15">
-        <v>-15.5944055944056</v>
+        <v>-55.3</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2189,73 +2252,67 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>34.9</v>
+        <v>0.1</v>
       </c>
       <c r="V15">
-        <v>0.1343858298036196</v>
+        <v>0.01182033096926714</v>
       </c>
       <c r="W15">
-        <v>-0.3468118195956454</v>
+        <v>-0.8014492753623188</v>
       </c>
       <c r="X15">
-        <v>0.07920586331692614</v>
+        <v>0.07747925154739624</v>
       </c>
       <c r="Y15">
-        <v>-0.4260176829125716</v>
+        <v>-0.878928526909715</v>
       </c>
       <c r="Z15">
-        <v>0.01988873435326843</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>-0.1835883171070932</v>
+        <v>-0.1158951832359482</v>
       </c>
       <c r="AB15">
-        <v>0.07859389322757537</v>
+        <v>0.068200496816426</v>
       </c>
       <c r="AC15">
-        <v>-0.2621822103346685</v>
+        <v>-0.1840956800523742</v>
       </c>
       <c r="AD15">
-        <v>6.8</v>
+        <v>3.87</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>6.8</v>
+        <v>3.87</v>
       </c>
       <c r="AG15">
-        <v>-28.1</v>
+        <v>3.77</v>
       </c>
       <c r="AH15">
-        <v>0.02551594746716698</v>
+        <v>0.3138686131386861</v>
       </c>
       <c r="AI15">
-        <v>0.1416666666666667</v>
+        <v>0.2008303061754022</v>
       </c>
       <c r="AJ15">
-        <v>-0.1213298791018998</v>
+        <v>0.3082583810302535</v>
       </c>
       <c r="AK15">
-        <v>-2.14503816793893</v>
+        <v>0.1966614501825769</v>
       </c>
       <c r="AL15">
-        <v>0.916</v>
+        <v>0.534</v>
       </c>
       <c r="AM15">
-        <v>0.907</v>
-      </c>
-      <c r="AN15">
-        <v>-0.5190839694656488</v>
+        <v>-0.146</v>
       </c>
       <c r="AO15">
-        <v>-14.41048034934498</v>
-      </c>
-      <c r="AP15">
-        <v>2.145038167938931</v>
+        <v>-15.71161048689139</v>
       </c>
       <c r="AQ15">
-        <v>-14.55347298787211</v>
+        <v>57.46575342465753</v>
       </c>
     </row>
     <row r="16">
@@ -2266,7 +2323,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>China Financial International Investments Limited (SEHK:721)</t>
+          <t>China Development Bank International Investment Limited (SEHK:1062)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2275,7 +2332,7 @@
         </is>
       </c>
       <c r="K16">
-        <v>-27.4</v>
+        <v>-21.3</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2299,73 +2356,64 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>5.05</v>
+        <v>4.66</v>
       </c>
       <c r="V16">
-        <v>0.09960552268244575</v>
+        <v>0.1527868852459016</v>
       </c>
       <c r="W16">
-        <v>-0.2660194174757282</v>
+        <v>-0.1130573248407643</v>
       </c>
       <c r="X16">
-        <v>0.07920747068752179</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y16">
-        <v>-0.34522688816325</v>
+        <v>-0.1798458521911762</v>
       </c>
       <c r="Z16">
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>-0.2633813143981785</v>
+        <v>-0.1318822709483729</v>
       </c>
       <c r="AB16">
-        <v>0.07859435078107756</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC16">
-        <v>-0.3419756651792561</v>
+        <v>-0.1986707982987848</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>-3.72</v>
+        <v>-4.66</v>
       </c>
       <c r="AH16">
-        <v>0.02556217566788391</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.01789317906632585</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.07918263090676883</v>
+        <v>-0.1803405572755418</v>
       </c>
       <c r="AK16">
-        <v>-0.05369515011547343</v>
+        <v>-0.02863463192822908</v>
       </c>
       <c r="AL16">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.095</v>
-      </c>
-      <c r="AN16">
-        <v>-0.04889705882352942</v>
-      </c>
-      <c r="AO16">
-        <v>-287.3684210526316</v>
-      </c>
-      <c r="AP16">
-        <v>0.1367647058823529</v>
+        <v>-2.23</v>
       </c>
       <c r="AQ16">
-        <v>-287.3684210526316</v>
+        <v>11.03139013452915</v>
       </c>
     </row>
     <row r="17">
@@ -2376,7 +2424,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cocoon Holdings Limited (SEHK:428)</t>
+          <t>China Vered Financial Holding Corporation Limited (SEHK:245)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2384,8 +2432,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D17">
+        <v>-0.216</v>
+      </c>
+      <c r="G17">
+        <v>-3.687179487179487</v>
+      </c>
+      <c r="H17">
+        <v>-3.687179487179487</v>
+      </c>
+      <c r="I17">
+        <v>-3.630769230769231</v>
+      </c>
+      <c r="J17">
+        <v>-3.630769230769231</v>
+      </c>
       <c r="K17">
-        <v>-7.56</v>
+        <v>-46</v>
+      </c>
+      <c r="L17">
+        <v>-2.358974358974359</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2409,73 +2475,73 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.027</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V17">
-        <v>0.0006553398058252427</v>
+        <v>0.5016077170418006</v>
       </c>
       <c r="W17">
-        <v>-0.336</v>
+        <v>-0.08318264014466546</v>
       </c>
       <c r="X17">
-        <v>0.08020055462720378</v>
+        <v>0.06726946204546198</v>
       </c>
       <c r="Y17">
-        <v>-0.4162005546272037</v>
+        <v>-0.1504521021901274</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>0.03938836932151009</v>
       </c>
       <c r="AA17">
-        <v>-0.2907527221082531</v>
+        <v>-0.1430100793827135</v>
       </c>
       <c r="AB17">
-        <v>0.07886897916171554</v>
+        <v>0.06704800844211631</v>
       </c>
       <c r="AC17">
-        <v>-0.3696217012699687</v>
+        <v>-0.2100580878248298</v>
       </c>
       <c r="AD17">
-        <v>2.32</v>
+        <v>3.84</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.32</v>
+        <v>3.84</v>
       </c>
       <c r="AG17">
-        <v>2.293</v>
+        <v>-89.75999999999999</v>
       </c>
       <c r="AH17">
-        <v>0.05330882352941176</v>
+        <v>0.0201638311279143</v>
       </c>
       <c r="AI17">
-        <v>0.1412911084043849</v>
+        <v>0.007480422332177504</v>
       </c>
       <c r="AJ17">
-        <v>0.05272112753776469</v>
+        <v>-0.9268897149938041</v>
       </c>
       <c r="AK17">
-        <v>0.1398767766729702</v>
+        <v>-0.2138466669843236</v>
       </c>
       <c r="AL17">
-        <v>0.19</v>
+        <v>0.114</v>
       </c>
       <c r="AM17">
-        <v>0.19</v>
+        <v>0.114</v>
       </c>
       <c r="AN17">
-        <v>-0.3147896879240162</v>
+        <v>-0.05439093484419263</v>
       </c>
       <c r="AO17">
-        <v>-38.78947368421053</v>
+        <v>-621.0526315789473</v>
       </c>
       <c r="AP17">
-        <v>-0.3111261872455902</v>
+        <v>1.271388101983003</v>
       </c>
       <c r="AQ17">
-        <v>-38.78947368421053</v>
+        <v>-621.0526315789473</v>
       </c>
     </row>
     <row r="18">
@@ -2486,7 +2552,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>China Internet Investment Finance Holdings Limited (SEHK:810)</t>
+          <t>OCI International Holdings Limited (SEHK:329)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2495,25 +2561,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.314</v>
+        <v>-0.159</v>
       </c>
       <c r="G18">
-        <v>-32.43243243243244</v>
+        <v>-0.9334203655352481</v>
       </c>
       <c r="H18">
-        <v>-32.43243243243244</v>
+        <v>-0.9334203655352481</v>
       </c>
       <c r="I18">
-        <v>-27.97297297297297</v>
+        <v>-0.3550913838120104</v>
       </c>
       <c r="J18">
-        <v>-27.97297297297297</v>
+        <v>-0.3550913838120104</v>
       </c>
       <c r="K18">
-        <v>-2.31</v>
+        <v>-3.33</v>
       </c>
       <c r="L18">
-        <v>-31.21621621621622</v>
+        <v>-0.4347258485639687</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2537,73 +2603,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>2.07</v>
+        <v>22.7</v>
       </c>
       <c r="V18">
-        <v>0.004856874706710464</v>
+        <v>0.2917737789203085</v>
       </c>
       <c r="W18">
-        <v>-0.21</v>
+        <v>-0.0808252427184466</v>
       </c>
       <c r="X18">
-        <v>0.07835505558371328</v>
+        <v>0.06961220281536531</v>
       </c>
       <c r="Y18">
-        <v>-0.2883550555837133</v>
+        <v>-0.1504374455338119</v>
       </c>
       <c r="Z18">
-        <v>0.01125304136253041</v>
+        <v>0.5847328244274809</v>
       </c>
       <c r="AA18">
-        <v>-0.3147810218978102</v>
+        <v>-0.2076335877862595</v>
       </c>
       <c r="AB18">
-        <v>0.07834545247532355</v>
+        <v>0.06751370882612472</v>
       </c>
       <c r="AC18">
-        <v>-0.3931264743731337</v>
+        <v>-0.2751472966123842</v>
       </c>
       <c r="AD18">
-        <v>0.177</v>
+        <v>9.4</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.177</v>
+        <v>9.4</v>
       </c>
       <c r="AG18">
-        <v>-1.893</v>
+        <v>-13.3</v>
       </c>
       <c r="AH18">
-        <v>0.0004151255813517145</v>
+        <v>0.1077981651376147</v>
       </c>
       <c r="AI18">
-        <v>0.02028188380886902</v>
+        <v>0.2012847965738758</v>
       </c>
       <c r="AJ18">
-        <v>-0.004461392340922963</v>
+        <v>-0.2062015503875969</v>
       </c>
       <c r="AK18">
-        <v>-0.284362325371789</v>
+        <v>-0.5541666666666666</v>
       </c>
       <c r="AL18">
-        <v>0.005</v>
+        <v>0.518</v>
       </c>
       <c r="AM18">
-        <v>0.005</v>
+        <v>0.421</v>
       </c>
       <c r="AN18">
-        <v>-0.08984771573604061</v>
+        <v>-3.574144486692016</v>
       </c>
       <c r="AO18">
-        <v>-413.9999999999999</v>
+        <v>-5.250965250965251</v>
       </c>
       <c r="AP18">
-        <v>0.9609137055837562</v>
+        <v>5.057034220532319</v>
       </c>
       <c r="AQ18">
-        <v>-413.9999999999999</v>
+        <v>-6.460807600950119</v>
       </c>
     </row>
     <row r="19">
@@ -2623,7 +2689,7 @@
         </is>
       </c>
       <c r="K19">
-        <v>-3.5</v>
+        <v>-3.39</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2647,31 +2713,31 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.326</v>
+        <v>0.093</v>
       </c>
       <c r="V19">
-        <v>0.0163</v>
+        <v>0.004285714285714286</v>
       </c>
       <c r="W19">
-        <v>-0.2348993288590604</v>
+        <v>-0.2548872180451128</v>
       </c>
       <c r="X19">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y19">
-        <v>-0.3132406725401708</v>
+        <v>-0.3216757453955246</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>-0.3210484651244613</v>
+        <v>-0.2651456759673192</v>
       </c>
       <c r="AB19">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC19">
-        <v>-0.3993898088055717</v>
+        <v>-0.331934203317731</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -2683,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>-0.326</v>
+        <v>-0.093</v>
       </c>
       <c r="AH19">
         <v>0</v>
@@ -2692,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="AJ19">
-        <v>-0.01657009250787842</v>
+        <v>-0.00430416068866571</v>
       </c>
       <c r="AK19">
-        <v>-0.02512717743178665</v>
+        <v>-0.009463722397476341</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2712,7 +2778,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>China Investment Development Limited (SEHK:204)</t>
+          <t>Capital VC Limited (SEHK:2324)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2720,26 +2786,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.472</v>
-      </c>
-      <c r="G20">
-        <v>-3.078260869565218</v>
-      </c>
-      <c r="H20">
-        <v>-3.078260869565218</v>
-      </c>
-      <c r="I20">
-        <v>-6.286956521739131</v>
-      </c>
-      <c r="J20">
-        <v>-6.286956521739131</v>
-      </c>
       <c r="K20">
-        <v>-5.65</v>
-      </c>
-      <c r="L20">
-        <v>-4.91304347826087</v>
+        <v>-19</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2763,73 +2811,73 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0.555</v>
+        <v>4.22</v>
       </c>
       <c r="V20">
-        <v>0.02032967032967033</v>
+        <v>0.4784580498866213</v>
       </c>
       <c r="W20">
-        <v>-0.2344398340248963</v>
+        <v>-0.3177257525083612</v>
       </c>
       <c r="X20">
-        <v>0.08148582196432252</v>
+        <v>0.07807628139101838</v>
       </c>
       <c r="Y20">
-        <v>-0.3159256559892188</v>
+        <v>-0.3958020338993796</v>
       </c>
       <c r="Z20">
-        <v>0.05455407969639468</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>-0.3429791271347248</v>
+        <v>-0.2762156797882898</v>
       </c>
       <c r="AB20">
-        <v>0.07920201445007351</v>
+        <v>0.0682536678449627</v>
       </c>
       <c r="AC20">
-        <v>-0.4221811415847984</v>
+        <v>-0.3444693476332525</v>
       </c>
       <c r="AD20">
-        <v>2.6</v>
+        <v>4.26</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>2.6</v>
+        <v>4.26</v>
       </c>
       <c r="AG20">
-        <v>2.045</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AH20">
-        <v>0.08695652173913043</v>
+        <v>0.3256880733944954</v>
       </c>
       <c r="AI20">
-        <v>0.09090909090909091</v>
+        <v>0.09454061251664447</v>
       </c>
       <c r="AJ20">
-        <v>0.06968819219628557</v>
+        <v>0.004514672686230252</v>
       </c>
       <c r="AK20">
-        <v>0.07291852380103404</v>
+        <v>0.000979431929480902</v>
       </c>
       <c r="AL20">
-        <v>0.347</v>
+        <v>0.779</v>
       </c>
       <c r="AM20">
-        <v>0.347</v>
+        <v>0.779</v>
       </c>
       <c r="AN20">
-        <v>-0.359612724757953</v>
+        <v>-0.2550898203592815</v>
       </c>
       <c r="AO20">
-        <v>-20.835734870317</v>
+        <v>-21.4377406931964</v>
       </c>
       <c r="AP20">
-        <v>-0.2828492392807745</v>
+        <v>-0.002395209580838325</v>
       </c>
       <c r="AQ20">
-        <v>-20.835734870317</v>
+        <v>-21.4377406931964</v>
       </c>
     </row>
     <row r="21">
@@ -2840,7 +2888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Core Economy Investment Group Limited (SEHK:339)</t>
+          <t>Harbour Digital Asset Capital Limited (SEHK:913)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2848,26 +2896,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D21">
-        <v>-0.247</v>
-      </c>
-      <c r="G21">
-        <v>-31.42857142857143</v>
-      </c>
-      <c r="H21">
-        <v>-31.42857142857143</v>
-      </c>
-      <c r="I21">
-        <v>-28.28571428571428</v>
-      </c>
-      <c r="J21">
-        <v>-28.28571428571428</v>
-      </c>
       <c r="K21">
-        <v>-2.33</v>
-      </c>
-      <c r="L21">
-        <v>-66.57142857142857</v>
+        <v>-4.49</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2891,73 +2921,61 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.188</v>
+        <v>0.107</v>
       </c>
       <c r="V21">
-        <v>0.04486873508353222</v>
+        <v>0.003862815884476534</v>
       </c>
       <c r="W21">
-        <v>-0.5796019900497513</v>
+        <v>-0.1886554621848739</v>
       </c>
       <c r="X21">
-        <v>0.08178488511369245</v>
+        <v>0.0668383055020334</v>
       </c>
       <c r="Y21">
-        <v>-0.6613868751634437</v>
+        <v>-0.2554937676869073</v>
       </c>
       <c r="Z21">
-        <v>0.01282051282051282</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>-0.3626373626373627</v>
+        <v>-0.3001776198934281</v>
       </c>
       <c r="AB21">
-        <v>0.08184704455628308</v>
+        <v>0.0668028256215351</v>
       </c>
       <c r="AC21">
-        <v>-0.4444844071936458</v>
+        <v>-0.3669804455149632</v>
       </c>
       <c r="AD21">
-        <v>0.437</v>
+        <v>0.059</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0.437</v>
+        <v>0.059</v>
       </c>
       <c r="AG21">
-        <v>0.249</v>
+        <v>-0.048</v>
       </c>
       <c r="AH21">
-        <v>0.0944456451264318</v>
+        <v>0.002125436795273605</v>
       </c>
       <c r="AI21">
-        <v>0.2103996148290804</v>
+        <v>0.003032016033711907</v>
       </c>
       <c r="AJ21">
-        <v>0.05609371480063077</v>
+        <v>-0.0017358599739621</v>
       </c>
       <c r="AK21">
-        <v>0.1318157755426151</v>
+        <v>-0.002480363786688714</v>
       </c>
       <c r="AL21">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AN21">
-        <v>-0.4528497409326425</v>
-      </c>
-      <c r="AO21">
-        <v>-14.14285714285714</v>
-      </c>
-      <c r="AP21">
-        <v>-0.2580310880829015</v>
-      </c>
-      <c r="AQ21">
-        <v>-14.14285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2968,7 +2986,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Somerley Capital Holdings Limited (SEHK:8439)</t>
+          <t>Sheng Yuan Holdings Limited (SEHK:851)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2977,118 +2995,115 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.0418</v>
+        <v>-0.0219</v>
       </c>
       <c r="G22">
-        <v>-0.04537037037037037</v>
+        <v>0.2359872611464968</v>
       </c>
       <c r="H22">
-        <v>-0.04537037037037037</v>
+        <v>0.2359872611464968</v>
       </c>
       <c r="I22">
-        <v>-0.2288359788359788</v>
+        <v>-0.9044585987261146</v>
       </c>
       <c r="J22">
-        <v>-0.2288359788359788</v>
+        <v>-0.9044585987261146</v>
       </c>
       <c r="K22">
-        <v>-1.69</v>
+        <v>-3.59</v>
       </c>
       <c r="L22">
-        <v>-0.2235449735449735</v>
+        <v>-1.143312101910828</v>
       </c>
       <c r="M22">
-        <v>0.453</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.02359375</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>-0.2680473372781065</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>0.453</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.02359375</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>-0.2680473372781065</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>8.4</v>
+        <v>8.82</v>
       </c>
       <c r="V22">
-        <v>0.4375000000000001</v>
+        <v>0.247752808988764</v>
       </c>
       <c r="W22">
-        <v>-0.1330708661417323</v>
+        <v>1.055882352941176</v>
       </c>
       <c r="X22">
-        <v>0.08097238761964179</v>
+        <v>0.06686730404817898</v>
       </c>
       <c r="Y22">
-        <v>-0.2140432537613741</v>
+        <v>0.9890150488929975</v>
       </c>
       <c r="Z22">
-        <v>1.654266958424508</v>
+        <v>0.4099216710182769</v>
       </c>
       <c r="AA22">
-        <v>-0.3785557986870897</v>
+        <v>-0.370757180156658</v>
       </c>
       <c r="AB22">
-        <v>0.07907185512249514</v>
+        <v>0.06681112717815554</v>
       </c>
       <c r="AC22">
-        <v>-0.4576276538095848</v>
+        <v>-0.4375683073348136</v>
       </c>
       <c r="AD22">
-        <v>1.53</v>
+        <v>0.12</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.53</v>
+        <v>0.12</v>
       </c>
       <c r="AG22">
-        <v>-6.87</v>
+        <v>-8.700000000000001</v>
       </c>
       <c r="AH22">
-        <v>0.07380607814761216</v>
+        <v>0.003359462486002239</v>
       </c>
       <c r="AI22">
-        <v>0.1271820448877806</v>
+        <v>0.009819967266775777</v>
       </c>
       <c r="AJ22">
-        <v>-0.5571776155717763</v>
+        <v>-0.3234200743494424</v>
       </c>
       <c r="AK22">
-        <v>-1.892561983471075</v>
+        <v>-2.558823529411766</v>
       </c>
       <c r="AL22">
-        <v>0.048</v>
+        <v>1.08</v>
       </c>
       <c r="AM22">
-        <v>0.048</v>
+        <v>1.08</v>
       </c>
       <c r="AN22">
-        <v>-0.9444444444444444</v>
+        <v>-0.04347826086956522</v>
       </c>
       <c r="AO22">
-        <v>-36.04166666666666</v>
+        <v>-2.629629629629629</v>
       </c>
       <c r="AP22">
-        <v>4.24074074074074</v>
+        <v>3.152173913043479</v>
       </c>
       <c r="AQ22">
-        <v>-36.04166666666666</v>
+        <v>-2.629629629629629</v>
       </c>
     </row>
     <row r="23">
@@ -3099,7 +3114,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AP Acquisition Corp. (NYSE:APCA)</t>
+          <t>China Castson 81 Finance Company Limited (SEHK:810)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3107,8 +3122,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D23">
+        <v>-0.391</v>
+      </c>
+      <c r="G23">
+        <v>-47.95454545454545</v>
+      </c>
+      <c r="H23">
+        <v>-47.95454545454545</v>
+      </c>
+      <c r="I23">
+        <v>-59.09090909090909</v>
+      </c>
+      <c r="J23">
+        <v>-59.09090909090909</v>
+      </c>
       <c r="K23">
-        <v>0.049</v>
+        <v>-0.503</v>
+      </c>
+      <c r="L23">
+        <v>-11.43181818181818</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3117,7 +3150,7 @@
         <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3126,70 +3159,79 @@
         <v>-0</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>0.366</v>
+        <v>1.74</v>
       </c>
       <c r="V23">
-        <v>0.001644943820224719</v>
+        <v>0.2134969325153374</v>
       </c>
       <c r="W23">
-        <v>-49</v>
+        <v>-0.05883040935672514</v>
       </c>
       <c r="X23">
-        <v>0.0783413436811104</v>
+        <v>0.06710682387280113</v>
       </c>
       <c r="Y23">
-        <v>-49.07834134368111</v>
+        <v>-0.1259372332295263</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>0.006609583896650143</v>
       </c>
       <c r="AA23">
-        <v>-8.14516129032258</v>
+        <v>-0.3905663211656903</v>
       </c>
       <c r="AB23">
-        <v>0.0783413436811104</v>
+        <v>0.0668789184542105</v>
       </c>
       <c r="AC23">
-        <v>-8.22350263400369</v>
+        <v>-0.4574452396199008</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AG23">
-        <v>-0.366</v>
+        <v>-1.629</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>0.01343662994794819</v>
       </c>
       <c r="AI23">
-        <v>-0</v>
+        <v>0.0135846285644352</v>
       </c>
       <c r="AJ23">
-        <v>-0.001647654118685118</v>
+        <v>-0.2498083116086489</v>
       </c>
       <c r="AK23">
-        <v>0.06023699802501646</v>
+        <v>-0.2533043072617011</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM23">
-        <v>-1.06</v>
+        <v>0.004</v>
+      </c>
+      <c r="AN23">
+        <v>-0.04387351778656127</v>
+      </c>
+      <c r="AO23">
+        <v>-650</v>
+      </c>
+      <c r="AP23">
+        <v>0.6438735177865613</v>
       </c>
       <c r="AQ23">
-        <v>0.9528301886792453</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="24">
@@ -3200,7 +3242,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>True Partner Capital Holding Limited (SEHK:8657)</t>
+          <t>Core Economy Investment Group Limited (SEHK:339)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3208,23 +3250,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D24">
+        <v>-0.344</v>
+      </c>
       <c r="G24">
-        <v>-0.4042553191489362</v>
+        <v>-38.84615384615385</v>
       </c>
       <c r="H24">
-        <v>-0.4042553191489362</v>
+        <v>-38.84615384615385</v>
       </c>
       <c r="I24">
-        <v>-0.5617719871774672</v>
+        <v>-40</v>
       </c>
       <c r="J24">
-        <v>-0.5617719871774672</v>
+        <v>-40</v>
       </c>
       <c r="K24">
-        <v>-3.9</v>
+        <v>-0.954</v>
       </c>
       <c r="L24">
-        <v>-0.5927051671732523</v>
+        <v>-36.69230769230769</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3248,67 +3293,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>0.002071428571428572</v>
+      </c>
+      <c r="W24">
+        <v>-0.5817073170731707</v>
       </c>
       <c r="X24">
-        <v>0.07874794384476688</v>
+        <v>0.06757644437893641</v>
+      </c>
+      <c r="Y24">
+        <v>-0.6492837614521071</v>
       </c>
       <c r="Z24">
-        <v>241.0399609300854</v>
+        <v>0.01376389624139756</v>
       </c>
       <c r="AA24">
-        <v>-135.4094978408731</v>
+        <v>-0.5505558496559027</v>
       </c>
       <c r="AB24">
-        <v>0.07842315018723649</v>
+        <v>0.06700793349088249</v>
       </c>
       <c r="AC24">
-        <v>-135.4879209910604</v>
+        <v>-0.6175637831467852</v>
       </c>
       <c r="AD24">
-        <v>0.485</v>
+        <v>0.472</v>
       </c>
       <c r="AE24">
-        <v>0.02729837813867119</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>0.5122983781386712</v>
+        <v>0.472</v>
       </c>
       <c r="AG24">
-        <v>0.5122983781386712</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="AH24">
-        <v>0.01216505386475451</v>
+        <v>0.0326147042564953</v>
       </c>
       <c r="AI24">
-        <v>0.02178852827994891</v>
+        <v>0.4068965517241379</v>
       </c>
       <c r="AJ24">
-        <v>0.01216505386475451</v>
+        <v>0.03067229799903067</v>
       </c>
       <c r="AK24">
-        <v>0.02178852827994891</v>
+        <v>0.3916887709991159</v>
       </c>
       <c r="AL24">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="AM24">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="AN24">
-        <v>-0.1401329095637099</v>
+        <v>-0.4627450980392157</v>
       </c>
       <c r="AO24">
-        <v>-265.7142857142857</v>
+        <v>-52</v>
       </c>
       <c r="AP24">
-        <v>-0.1480203346254467</v>
+        <v>-0.434313725490196</v>
       </c>
       <c r="AQ24">
-        <v>-265.7142857142857</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="25">
@@ -3328,16 +3379,16 @@
         </is>
       </c>
       <c r="K25">
-        <v>12.2</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>380.5</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>2.443802183686577</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>-675.8436944937833</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3346,61 +3397,64 @@
         <v>-0</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>380.5</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0.293</v>
+        <v>0.123</v>
       </c>
       <c r="V25">
-        <v>0.0005600152905198775</v>
+        <v>0.000789980732177264</v>
       </c>
       <c r="W25">
-        <v>-0.431095406360424</v>
+        <v>0.03026881720430107</v>
       </c>
       <c r="X25">
-        <v>0.07837289664553485</v>
+        <v>0.0672028006974366</v>
       </c>
       <c r="Y25">
-        <v>-0.5094683030059588</v>
+        <v>-0.03693398349313554</v>
       </c>
       <c r="AB25">
-        <v>0.07835079347473566</v>
+        <v>0.06690569959880981</v>
       </c>
       <c r="AD25">
-        <v>0.5</v>
+        <v>2.76</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.5</v>
+        <v>2.76</v>
       </c>
       <c r="AG25">
-        <v>0.207</v>
+        <v>2.637</v>
       </c>
       <c r="AH25">
-        <v>0.0009547450830628221</v>
+        <v>0.01741764483150322</v>
       </c>
       <c r="AI25">
-        <v>-0.02762430939226519</v>
+        <v>-0.2183544303797468</v>
       </c>
       <c r="AJ25">
-        <v>0.0003954857309894594</v>
+        <v>0.01665435116239413</v>
       </c>
       <c r="AK25">
-        <v>-0.01125428152014353</v>
+        <v>-0.2066128653137976</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-2.5</v>
+        <v>-7.11</v>
       </c>
       <c r="AQ25">
-        <v>1.452</v>
+        <v>0.549929676511955</v>
       </c>
     </row>
     <row r="26">
@@ -3411,7 +3465,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primavera Capital Acquisition Corporation</t>
+          <t>Magnum Opus Acquisition Limited (NYSE:OPA)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3420,16 +3474,16 @@
         </is>
       </c>
       <c r="K26">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>137.1</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>1.095923261390887</v>
       </c>
       <c r="O26">
-        <v>-0</v>
+        <v>8.845161290322581</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3441,58 +3495,61 @@
         <v>-0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>137.1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>0.059</v>
+        <v>0.517</v>
       </c>
       <c r="V26">
-        <v>0.000120359037127703</v>
+        <v>0.004132693844924061</v>
       </c>
       <c r="W26">
-        <v>-0.4455445544554456</v>
+        <v>-0.5893536121673003</v>
       </c>
       <c r="X26">
-        <v>0.07837071010620331</v>
+        <v>0.06686269247330569</v>
       </c>
       <c r="Y26">
-        <v>-0.5239152645616488</v>
+        <v>-0.656216304640606</v>
       </c>
       <c r="AB26">
-        <v>0.07834160602067695</v>
+        <v>0.06678740617154309</v>
       </c>
       <c r="AD26">
-        <v>0.436</v>
+        <v>0.397</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0.436</v>
+        <v>0.397</v>
       </c>
       <c r="AG26">
-        <v>0.377</v>
+        <v>-0.12</v>
       </c>
       <c r="AH26">
-        <v>0.0008886424966777815</v>
+        <v>0.003163422233200794</v>
       </c>
       <c r="AI26">
-        <v>-0.01782210595160235</v>
+        <v>-0.02940087387987855</v>
       </c>
       <c r="AJ26">
-        <v>0.0007684828273645116</v>
+        <v>-0.0009601536245799329</v>
       </c>
       <c r="AK26">
-        <v>-0.01537332300289524</v>
+        <v>0.008559201141226819</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-2.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AQ26">
-        <v>2.656</v>
+        <v>1.034042553191489</v>
       </c>
     </row>
     <row r="27">
@@ -3503,7 +3560,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bridgetown Holdings Limited (NasdaqCM:BTWN)</t>
+          <t>True Partner Capital Holding Limited (SEHK:8657)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3511,8 +3568,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G27">
+        <v>-1.393617021276596</v>
+      </c>
+      <c r="H27">
+        <v>-1.393617021276596</v>
+      </c>
+      <c r="I27">
+        <v>-2.553191489361702</v>
+      </c>
+      <c r="J27">
+        <v>-2.553191489361702</v>
+      </c>
       <c r="K27">
-        <v>32.1</v>
+        <v>-7.2</v>
+      </c>
+      <c r="L27">
+        <v>-2.553191489361702</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3521,7 +3593,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3530,61 +3602,64 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>0.0007407407407407407</v>
-      </c>
-      <c r="W27">
-        <v>-0.602251407129456</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>0.07858813758273221</v>
-      </c>
-      <c r="Y27">
-        <v>-0.6808395447121882</v>
+        <v>0.06713174511768856</v>
       </c>
       <c r="AB27">
-        <v>0.07834353395826979</v>
+        <v>0.06688589325590996</v>
       </c>
       <c r="AD27">
-        <v>2.22</v>
+        <v>0.304</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.22</v>
+        <v>0.304</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>0.304</v>
       </c>
       <c r="AH27">
-        <v>0.007419290154401444</v>
+        <v>0.0144734336316892</v>
       </c>
       <c r="AI27">
-        <v>-0.09536082474226805</v>
+        <v>0.01767030923041154</v>
       </c>
       <c r="AJ27">
-        <v>0.006688963210702341</v>
+        <v>0.0144734336316892</v>
       </c>
       <c r="AK27">
-        <v>-0.0851063829787234</v>
+        <v>0.01767030923041154</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM27">
-        <v>-3.9</v>
+        <v>0.018</v>
+      </c>
+      <c r="AN27">
+        <v>-0.04349070100143061</v>
+      </c>
+      <c r="AO27">
+        <v>-400.0000000000001</v>
+      </c>
+      <c r="AP27">
+        <v>-0.04349070100143061</v>
       </c>
       <c r="AQ27">
-        <v>0.3948717948717949</v>
+        <v>-400.0000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3595,7 +3670,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Summit Healthcare Acquisition Corp. (NasdaqCM:SMIH)</t>
+          <t>Zijing International Financial Holdings Limited (SEHK:8340)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3603,8 +3678,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D28">
+        <v>-0.126</v>
+      </c>
+      <c r="G28">
+        <v>-0.5366279069767442</v>
+      </c>
+      <c r="H28">
+        <v>-0.5366279069767442</v>
+      </c>
+      <c r="I28">
+        <v>-0.6569767441860465</v>
+      </c>
+      <c r="J28">
+        <v>-0.6569767441860465</v>
+      </c>
       <c r="K28">
-        <v>17.7</v>
+        <v>-1.14</v>
+      </c>
+      <c r="L28">
+        <v>-0.6627906976744186</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3613,7 +3706,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3622,931 +3715,64 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>0.0002712127082526153</v>
-      </c>
-      <c r="W28">
-        <v>-0.7901785714285714</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>0.0783413436811104</v>
-      </c>
-      <c r="Y28">
-        <v>-0.8685199151096819</v>
+        <v>0.0730087913185927</v>
       </c>
       <c r="AB28">
-        <v>0.0783413436811104</v>
+        <v>0.06949364695227481</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AG28">
-        <v>-0.07000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.2102102102102102</v>
       </c>
       <c r="AI28">
-        <v>-0</v>
+        <v>0.1939058171745152</v>
       </c>
       <c r="AJ28">
-        <v>-0.0002712862845405573</v>
+        <v>0.2102102102102102</v>
       </c>
       <c r="AK28">
-        <v>0.01158940397350993</v>
+        <v>0.1939058171745152</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="AM28">
-        <v>-1.2</v>
+        <v>0.039</v>
+      </c>
+      <c r="AN28">
+        <v>-0.6542056074766355</v>
+      </c>
+      <c r="AO28">
+        <v>-28.97435897435897</v>
+      </c>
+      <c r="AP28">
+        <v>-0.6542056074766355</v>
       </c>
       <c r="AQ28">
-        <v>1.275</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Magnum Opus Acquisition Limited (NYSE:OPA)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K29">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="M29">
-        <v>-0</v>
-      </c>
-      <c r="N29">
-        <v>-0</v>
-      </c>
-      <c r="O29">
-        <v>-0</v>
-      </c>
-      <c r="P29">
-        <v>-0</v>
-      </c>
-      <c r="Q29">
-        <v>-0</v>
-      </c>
-      <c r="R29">
-        <v>-0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0.025</v>
-      </c>
-      <c r="V29">
-        <v>9.920634920634921e-05</v>
-      </c>
-      <c r="W29">
-        <v>-0.3882113821138212</v>
-      </c>
-      <c r="X29">
-        <v>0.07836649950737611</v>
-      </c>
-      <c r="Y29">
-        <v>-0.4665778816211973</v>
-      </c>
-      <c r="AB29">
-        <v>0.07834887905518202</v>
-      </c>
-      <c r="AD29">
-        <v>0.192</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0.192</v>
-      </c>
-      <c r="AG29">
-        <v>0.167</v>
-      </c>
-      <c r="AH29">
-        <v>0.0007613247049866769</v>
-      </c>
-      <c r="AI29">
-        <v>-0.01351351351351351</v>
-      </c>
-      <c r="AJ29">
-        <v>0.0006622595343562005</v>
-      </c>
-      <c r="AK29">
-        <v>-0.01173329586172978</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1.17</v>
-      </c>
-      <c r="AQ29">
-        <v>6.700854700854701</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Black Spade Acquisition Co (NYSE:BSAQ)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K30">
-        <v>1.84</v>
-      </c>
-      <c r="M30">
-        <v>-0</v>
-      </c>
-      <c r="N30">
-        <v>-0</v>
-      </c>
-      <c r="O30">
-        <v>-0</v>
-      </c>
-      <c r="P30">
-        <v>-0</v>
-      </c>
-      <c r="Q30">
-        <v>-0</v>
-      </c>
-      <c r="R30">
-        <v>-0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0.074</v>
-      </c>
-      <c r="V30">
-        <v>0.0003502129673450071</v>
-      </c>
-      <c r="W30">
-        <v>-0.1520661157024794</v>
-      </c>
-      <c r="X30">
-        <v>0.07834165619433306</v>
-      </c>
-      <c r="Y30">
-        <v>-0.2304077718968124</v>
-      </c>
-      <c r="AB30">
-        <v>0.07834134647534655</v>
-      </c>
-      <c r="AD30">
-        <v>0.002</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0.002</v>
-      </c>
-      <c r="AG30">
-        <v>-0.07199999999999999</v>
-      </c>
-      <c r="AH30">
-        <v>9.465125744195511e-06</v>
-      </c>
-      <c r="AI30">
-        <v>-0.0001980590215884334</v>
-      </c>
-      <c r="AJ30">
-        <v>-0.000340863900619236</v>
-      </c>
-      <c r="AK30">
-        <v>0.007078254030672434</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>-1.01</v>
-      </c>
-      <c r="AQ30">
-        <v>6.455445544554455</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Aquila Acquisition Corporation (SEHK:7836)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K31">
-        <v>-0.144</v>
-      </c>
-      <c r="M31">
-        <v>-0</v>
-      </c>
-      <c r="N31">
-        <v>-0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>-0</v>
-      </c>
-      <c r="Q31">
-        <v>-0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>1.34</v>
-      </c>
-      <c r="V31">
-        <v>0.009279778393351801</v>
-      </c>
-      <c r="X31">
-        <v>0.07836237945688315</v>
-      </c>
-      <c r="AB31">
-        <v>0.07834764568865107</v>
-      </c>
-      <c r="AD31">
-        <v>0.092</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0.092</v>
-      </c>
-      <c r="AG31">
-        <v>-1.248</v>
-      </c>
-      <c r="AH31">
-        <v>0.0006367134512637377</v>
-      </c>
-      <c r="AI31">
-        <v>-0.02306920762286861</v>
-      </c>
-      <c r="AJ31">
-        <v>-0.008718006035542639</v>
-      </c>
-      <c r="AK31">
-        <v>0.2342342342342342</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Blue Safari Group Acquisition Corp. (NasdaqCM:BSGA)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K32">
-        <v>-4.49</v>
-      </c>
-      <c r="M32">
-        <v>-0</v>
-      </c>
-      <c r="N32">
-        <v>-0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>-0</v>
-      </c>
-      <c r="Q32">
-        <v>-0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0.359</v>
-      </c>
-      <c r="V32">
-        <v>0.004573248407643312</v>
-      </c>
-      <c r="W32">
-        <v>2.641176470588236</v>
-      </c>
-      <c r="X32">
-        <v>0.07926245550432649</v>
-      </c>
-      <c r="Y32">
-        <v>2.561914015083909</v>
-      </c>
-      <c r="AB32">
-        <v>0.07834935605335401</v>
-      </c>
-      <c r="AD32">
-        <v>2.19</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>2.19</v>
-      </c>
-      <c r="AG32">
-        <v>1.831</v>
-      </c>
-      <c r="AH32">
-        <v>0.02714090965423225</v>
-      </c>
-      <c r="AI32">
-        <v>-0.4171428571428571</v>
-      </c>
-      <c r="AJ32">
-        <v>0.0227931931632869</v>
-      </c>
-      <c r="AK32">
-        <v>-0.3264396505615974</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>-0.352</v>
-      </c>
-      <c r="AQ32">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Malacca Straits Acquisition Company Limited (NasdaqCM:MLAC)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K33">
-        <v>3.15</v>
-      </c>
-      <c r="M33">
-        <v>96.8</v>
-      </c>
-      <c r="N33">
-        <v>2.310262529832936</v>
-      </c>
-      <c r="O33">
-        <v>30.73015873015873</v>
-      </c>
-      <c r="P33">
-        <v>-0</v>
-      </c>
-      <c r="Q33">
-        <v>-0</v>
-      </c>
-      <c r="R33">
-        <v>-0</v>
-      </c>
-      <c r="S33">
-        <v>96.8</v>
-      </c>
-      <c r="T33">
-        <v>1</v>
-      </c>
-      <c r="U33">
-        <v>0.203</v>
-      </c>
-      <c r="V33">
-        <v>0.004844868735083533</v>
-      </c>
-      <c r="W33">
-        <v>-0.3156312625250501</v>
-      </c>
-      <c r="X33">
-        <v>0.08045317229422708</v>
-      </c>
-      <c r="Y33">
-        <v>-0.3960844348192771</v>
-      </c>
-      <c r="AB33">
-        <v>0.07835909094668785</v>
-      </c>
-      <c r="AD33">
-        <v>2.68</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>2.68</v>
-      </c>
-      <c r="AG33">
-        <v>2.477</v>
-      </c>
-      <c r="AH33">
-        <v>0.06011664423508301</v>
-      </c>
-      <c r="AI33">
-        <v>-0.4710017574692443</v>
-      </c>
-      <c r="AJ33">
-        <v>0.05581720260495303</v>
-      </c>
-      <c r="AK33">
-        <v>-0.4203292041405058</v>
-      </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>-0.276</v>
-      </c>
-      <c r="AQ33">
-        <v>4.637681159420289</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Model Performance Acquisition Corp. (NasdaqCM:MPAC)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K34">
-        <v>-1.58</v>
-      </c>
-      <c r="M34">
-        <v>36.3</v>
-      </c>
-      <c r="N34">
-        <v>1.186274509803921</v>
-      </c>
-      <c r="O34">
-        <v>-22.97468354430379</v>
-      </c>
-      <c r="P34">
-        <v>-0</v>
-      </c>
-      <c r="Q34">
-        <v>-0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>36.3</v>
-      </c>
-      <c r="T34">
-        <v>1</v>
-      </c>
-      <c r="U34">
-        <v>0.442</v>
-      </c>
-      <c r="V34">
-        <v>0.01444444444444444</v>
-      </c>
-      <c r="W34">
-        <v>0.9349112426035504</v>
-      </c>
-      <c r="X34">
-        <v>0.08124382044938905</v>
-      </c>
-      <c r="Y34">
-        <v>0.8536674221541614</v>
-      </c>
-      <c r="AB34">
-        <v>0.07914112890904292</v>
-      </c>
-      <c r="AD34">
-        <v>2.69</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>2.69</v>
-      </c>
-      <c r="AG34">
-        <v>2.248</v>
-      </c>
-      <c r="AH34">
-        <v>0.08080504656052868</v>
-      </c>
-      <c r="AI34">
-        <v>-1.174672489082969</v>
-      </c>
-      <c r="AJ34">
-        <v>0.06843643448611787</v>
-      </c>
-      <c r="AK34">
-        <v>-0.8228404099560759</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-0.338</v>
-      </c>
-      <c r="AQ34">
-        <v>5.857988165680473</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Goldstone Capital Group Limited (SEHK:1160)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>2.595</v>
-      </c>
-      <c r="G35">
-        <v>-4.915032679738562</v>
-      </c>
-      <c r="H35">
-        <v>-4.915032679738562</v>
-      </c>
-      <c r="I35">
-        <v>-6.535947712418301</v>
-      </c>
-      <c r="J35">
-        <v>-6.535947712418301</v>
-      </c>
-      <c r="K35">
-        <v>-1.01</v>
-      </c>
-      <c r="L35">
-        <v>-6.601307189542484</v>
-      </c>
-      <c r="M35">
-        <v>-0</v>
-      </c>
-      <c r="N35">
-        <v>-0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>-0</v>
-      </c>
-      <c r="Q35">
-        <v>-0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>3.61</v>
-      </c>
-      <c r="V35">
-        <v>0.1479508196721311</v>
-      </c>
-      <c r="W35">
-        <v>1.218335343787696</v>
-      </c>
-      <c r="X35">
-        <v>0.0790328067232651</v>
-      </c>
-      <c r="Y35">
-        <v>1.139302537064431</v>
-      </c>
-      <c r="AB35">
-        <v>0.07854437574621463</v>
-      </c>
-      <c r="AD35">
-        <v>0.511</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0.511</v>
-      </c>
-      <c r="AG35">
-        <v>-3.099</v>
-      </c>
-      <c r="AH35">
-        <v>0.02051302637389105</v>
-      </c>
-      <c r="AI35">
-        <v>0.1280380856928088</v>
-      </c>
-      <c r="AJ35">
-        <v>-0.1454861274118586</v>
-      </c>
-      <c r="AK35">
-        <v>-8.13385826771653</v>
-      </c>
-      <c r="AL35">
-        <v>0.017</v>
-      </c>
-      <c r="AM35">
-        <v>0.017</v>
-      </c>
-      <c r="AN35">
-        <v>-0.511</v>
-      </c>
-      <c r="AO35">
-        <v>-58.8235294117647</v>
-      </c>
-      <c r="AP35">
-        <v>3.099</v>
-      </c>
-      <c r="AQ35">
-        <v>-58.8235294117647</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Xenous Holdings, Inc. (OTCPK:XITO)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K36">
-        <v>-0.059</v>
-      </c>
-      <c r="M36">
-        <v>-0</v>
-      </c>
-      <c r="N36">
-        <v>-0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>-0</v>
-      </c>
-      <c r="Q36">
-        <v>-0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0.08613138686131386</v>
-      </c>
-      <c r="X36">
-        <v>0.08037785579276718</v>
-      </c>
-      <c r="Y36">
-        <v>0.005753531068546675</v>
-      </c>
-      <c r="AB36">
-        <v>0.07891637312236553</v>
-      </c>
-      <c r="AD36">
-        <v>0.734</v>
-      </c>
-      <c r="AE36">
-        <v>0</v>
-      </c>
-      <c r="AF36">
-        <v>0.734</v>
-      </c>
-      <c r="AG36">
-        <v>0.734</v>
-      </c>
-      <c r="AH36">
-        <v>0.0580971980370429</v>
-      </c>
-      <c r="AI36">
-        <v>-81.55555555555549</v>
-      </c>
-      <c r="AJ36">
-        <v>0.0580971980370429</v>
-      </c>
-      <c r="AK36">
-        <v>-81.55555555555549</v>
-      </c>
-      <c r="AL36">
-        <v>0</v>
-      </c>
-      <c r="AM36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Zijing International Financial Holdings Limited (SEHK:8340)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>-0.083</v>
-      </c>
-      <c r="G37">
-        <v>0.3088</v>
-      </c>
-      <c r="H37">
-        <v>0.3088</v>
-      </c>
-      <c r="I37">
-        <v>-0.0824</v>
-      </c>
-      <c r="J37">
-        <v>-0.0824</v>
-      </c>
-      <c r="K37">
-        <v>-0.201</v>
-      </c>
-      <c r="L37">
-        <v>-0.0804</v>
-      </c>
-      <c r="M37">
-        <v>-0</v>
-      </c>
-      <c r="N37">
-        <v>-0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>-0</v>
-      </c>
-      <c r="Q37">
-        <v>-0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0.09117481511966161</v>
-      </c>
-      <c r="AB37">
-        <v>0.0837526758000374</v>
-      </c>
-      <c r="AD37">
-        <v>1.1</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>1.1</v>
-      </c>
-      <c r="AG37">
-        <v>1.1</v>
-      </c>
-      <c r="AH37">
-        <v>0.2798982188295165</v>
-      </c>
-      <c r="AI37">
-        <v>0.222672064777328</v>
-      </c>
-      <c r="AJ37">
-        <v>0.2798982188295165</v>
-      </c>
-      <c r="AK37">
-        <v>0.222672064777328</v>
-      </c>
-      <c r="AL37">
-        <v>0.013</v>
-      </c>
-      <c r="AM37">
-        <v>0.013</v>
-      </c>
-      <c r="AN37">
-        <v>-4.741379310344827</v>
-      </c>
-      <c r="AO37">
-        <v>-15.84615384615385</v>
-      </c>
-      <c r="AP37">
-        <v>-4.741379310344827</v>
-      </c>
-      <c r="AQ37">
-        <v>-15.84615384615385</v>
+        <v>-28.97435897435897</v>
       </c>
     </row>
   </sheetData>
